--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -902,25 +902,21 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 2</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1086,25 +1082,21 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 17, not in English: 1</t>
-        </is>
-      </c>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1471,7 +1463,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -1485,7 +1477,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1688,25 +1680,21 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 3</t>
-        </is>
-      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1954,7 +1942,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -1968,7 +1956,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2033,10 +2021,14 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
@@ -2054,10 +2046,14 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.aviva.co.uk/</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.aviva.co.uk/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2208,25 +2204,25 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>older than limit: 4, experience: no entry-level signal: 3, experience: senior title: 3, outside Europe: 2</t>
+          <t>outside Europe: 2, experience: senior title: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2294,7 +2290,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2308,7 +2304,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2376,25 +2372,21 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2896,25 +2888,25 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>older than limit: 13, outside Europe: 2, not in English: 1, experience: requires 3+ yrs: 1</t>
+          <t>outside Europe: 2</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2982,25 +2974,25 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 4, older than limit: 3, outside Europe: 1</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3031,7 +3023,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>0</v>
@@ -3045,7 +3037,7 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3121,7 +3113,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3135,7 +3127,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3322,7 +3314,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3336,7 +3328,7 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3404,7 +3396,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3418,7 +3410,7 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3584,25 +3576,21 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 10+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3760,7 +3748,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>1</v>
@@ -3773,12 +3761,12 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 5+ yrs: 1</t>
+          <t>experience: requires 3-5 yrs: 1</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3809,25 +3797,21 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 3</t>
-        </is>
-      </c>
+      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3936,25 +3920,29 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3991,19 +3979,15 @@
         <v>2</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 2</t>
-        </is>
-      </c>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4183,7 +4167,7 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4210,25 +4194,29 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4255,29 +4243,25 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 2+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4494,19 +4478,15 @@
         <v>1</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>undated (first run): 1</t>
-        </is>
-      </c>
+      <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4537,25 +4517,21 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 2</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4877,7 +4853,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -4891,7 +4867,7 @@
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -5004,21 +4980,25 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 3, outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5100,19 +5080,15 @@
         <v>1</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5143,7 +5119,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>0</v>
@@ -5157,7 +5133,7 @@
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5426,12 +5402,12 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5767,7 +5743,7 @@
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -6052,7 +6028,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>0</v>
@@ -6066,7 +6042,7 @@
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6769,25 +6745,25 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 3+ yrs: 1, not in English: 1, older than limit: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6869,19 +6845,15 @@
         <v>7</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 4, experience: senior title: 2, experience: requires 3+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -6994,25 +6966,21 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 6</t>
-        </is>
-      </c>
+      <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7102,7 +7070,7 @@
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7813,25 +7781,25 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>21</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>older than limit: 20, experience: senior title: 1</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -7907,7 +7875,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>0</v>
@@ -7921,7 +7889,7 @@
       <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -8077,19 +8045,15 @@
         <v>4</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 4</t>
-        </is>
-      </c>
+      <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -8343,19 +8307,15 @@
         <v>2</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1, older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -8558,25 +8518,21 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>11</v>
       </c>
       <c r="G183" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I183" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 11</t>
-        </is>
-      </c>
+      <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8644,7 +8600,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>0</v>
@@ -8658,7 +8614,7 @@
       <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8732,19 +8688,15 @@
         <v>3</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I187" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 3</t>
-        </is>
-      </c>
+      <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -8789,7 +8741,7 @@
       <c r="I188" s="2" t="inlineStr"/>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -8820,25 +8772,21 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I189" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 6, experience: senior title: 2</t>
-        </is>
-      </c>
+      <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -8988,21 +8936,25 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F193" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H193" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -9121,19 +9073,15 @@
         <v>11</v>
       </c>
       <c r="G196" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I196" s="2" t="inlineStr">
-        <is>
-          <t>undated (first run): 11</t>
-        </is>
-      </c>
+      <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -9432,7 +9380,7 @@
       <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -9463,7 +9411,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>0</v>
@@ -9477,7 +9425,7 @@
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -9821,7 +9769,7 @@
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -9942,25 +9890,21 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F215" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G215" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I215" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 11</t>
-        </is>
-      </c>
+      <c r="I215" s="2" t="inlineStr"/>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -10028,25 +9972,25 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>older than limit: 25, outside Europe: 6, not in English: 1, experience: senior title: 1</t>
+          <t>experience: requires 2+ yrs: 1, experience: requires 5+ yrs: 1, outside Europe: 1</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -10638,25 +10582,21 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G231" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H231" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I231" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 9</t>
-        </is>
-      </c>
+      <c r="I231" s="2" t="inlineStr"/>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K231" s="2" t="inlineStr">
@@ -10735,22 +10675,18 @@
         <v>51</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G233" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H233" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I233" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 3, experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I233" s="2" t="inlineStr"/>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -10818,7 +10754,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -10832,7 +10768,7 @@
       <c r="I235" s="2" t="inlineStr"/>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr">
@@ -10903,18 +10839,22 @@
         <v>30</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -11080,25 +11020,21 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G241" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H241" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I241" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 3</t>
-        </is>
-      </c>
+      <c r="I241" s="2" t="inlineStr"/>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -11349,22 +11285,22 @@
         <v>319</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>older than limit: 28, outside Europe: 3, experience: requires 3-5 yrs: 1, experience: requires 12+ yrs: 1, experience: no entry-level signal: 1</t>
+          <t>outside Europe: 7, experience: no entry-level signal: 1, experience: requires 8+ yrs: 1</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K247" s="2" t="inlineStr">
@@ -11530,7 +11466,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11544,7 +11480,7 @@
       <c r="I251" s="2" t="inlineStr"/>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K251" s="2" t="inlineStr">
@@ -11784,25 +11720,21 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G257" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H257" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I257" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 2, older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I257" s="2" t="inlineStr"/>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr">
@@ -11878,25 +11810,25 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>older than limit: 5</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
@@ -12107,25 +12039,21 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I264" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 2, experience: requires 2+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I264" s="2" t="inlineStr"/>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
@@ -12398,25 +12326,29 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F271" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H271" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I271" s="2" t="inlineStr"/>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 1</t>
+        </is>
+      </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K271" s="2" t="inlineStr">
@@ -12955,7 +12887,7 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F284" s="2" t="n">
         <v>0</v>
@@ -12969,7 +12901,7 @@
       <c r="I284" s="2" t="inlineStr"/>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr">
@@ -13162,19 +13094,15 @@
         <v>4</v>
       </c>
       <c r="G289" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H289" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I289" s="2" t="inlineStr">
-        <is>
-          <t>undated (first run): 4</t>
-        </is>
-      </c>
+      <c r="I289" s="2" t="inlineStr"/>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr">
@@ -13764,7 +13692,7 @@
       <c r="I303" s="2" t="inlineStr"/>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr">
@@ -14161,7 +14089,7 @@
       <c r="I312" s="2" t="inlineStr"/>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K312" s="2" t="inlineStr">
@@ -14341,7 +14269,7 @@
       <c r="I316" s="2" t="inlineStr"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K316" s="2" t="inlineStr">
@@ -14632,7 +14560,7 @@
       <c r="I323" s="2" t="inlineStr"/>
       <c r="J323" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K323" s="2" t="inlineStr">
@@ -14663,7 +14591,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>0</v>
@@ -14677,7 +14605,7 @@
       <c r="I324" s="2" t="inlineStr"/>
       <c r="J324" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K324" s="2" t="inlineStr">
@@ -14708,7 +14636,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14722,7 +14650,7 @@
       <c r="I325" s="2" t="inlineStr"/>
       <c r="J325" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K325" s="2" t="inlineStr">
@@ -14749,29 +14677,25 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F326" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G326" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H326" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I326" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I326" s="2" t="inlineStr"/>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -14853,19 +14777,19 @@
         <v>39</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>older than limit: 35, outside Europe: 2, experience: senior title: 1, not in English: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K328" s="2" t="inlineStr">
@@ -14941,7 +14865,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>0</v>
@@ -14955,7 +14879,7 @@
       <c r="I330" s="2" t="inlineStr"/>
       <c r="J330" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K330" s="2" t="inlineStr">
@@ -14992,19 +14916,15 @@
         <v>1</v>
       </c>
       <c r="G331" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H331" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I331" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I331" s="2" t="inlineStr"/>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">
@@ -15080,10 +15000,10 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G333" s="2" t="n">
         <v>2</v>
@@ -15093,12 +15013,12 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 2</t>
+          <t>experience: requires 5+ yrs: 2</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K333" s="2" t="inlineStr">
@@ -15129,7 +15049,7 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>0</v>
@@ -15143,7 +15063,7 @@
       <c r="I334" s="2" t="inlineStr"/>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K334" s="2" t="inlineStr">

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>17</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>3</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
@@ -2046,7 +2046,7 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.aviva.co.uk/</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2204,20 +2204,20 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2, experience: senior title: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
@@ -2888,20 +2888,20 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>640</v>
+        <v>664</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2</t>
+          <t>outside Europe: 4, experience: internship: 1</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>1</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3023,18 +3023,22 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3064,25 +3068,29 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3113,7 +3121,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3314,7 +3322,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3396,7 +3404,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3576,7 +3584,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>1</v>
@@ -3748,10 +3756,10 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>1</v>
@@ -3761,7 +3769,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 3-5 yrs: 1</t>
+          <t>experience: requires 5+ yrs: 1</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -3797,7 +3805,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -3920,29 +3928,25 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3973,7 +3977,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>2</v>
@@ -4194,29 +4198,25 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>2</v>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -4980,22 +4980,18 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 3, outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5074,18 +5070,22 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 2+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5385,29 +5385,25 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -6323,25 +6319,29 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>4</v>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>not in English: 1</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>7</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>6</v>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G166" s="2" t="n">
         <v>1</v>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>11</v>
@@ -8600,7 +8600,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>0</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>3</v>
@@ -8936,22 +8936,18 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G193" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I193" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9411,18 +9407,22 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F204" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H204" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 3+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>10</v>
@@ -9975,17 +9975,17 @@
         <v>374</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 2+ yrs: 1, experience: requires 5+ yrs: 1, outside Europe: 1</t>
+          <t>outside Europe: 2</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -10582,18 +10582,22 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H231" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I231" s="2" t="inlineStr"/>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10672,10 +10676,10 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G233" s="2" t="n">
         <v>0</v>
@@ -10836,10 +10840,10 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G237" s="2" t="n">
         <v>1</v>
@@ -10849,7 +10853,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -11282,20 +11286,20 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 7, experience: no entry-level signal: 1, experience: requires 8+ yrs: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -11372,7 +11376,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E249" s="2" t="n">
@@ -11390,7 +11394,7 @@
       <c r="I249" s="2" t="inlineStr"/>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.rolls-royce.com/en</t>
         </is>
       </c>
       <c r="K249" s="2" t="inlineStr">
@@ -11466,7 +11470,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11720,7 +11724,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>3</v>
@@ -11810,22 +11814,18 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I259" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I259" s="2" t="inlineStr"/>
       <c r="J259" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12039,18 +12039,22 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F264" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I264" s="2" t="inlineStr"/>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12155,31 +12159,43 @@
           <t>Luxembourg</t>
         </is>
       </c>
-      <c r="C267" s="2" t="inlineStr"/>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>successfactors</t>
+        </is>
+      </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I267" s="2" t="inlineStr"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 6-10 yrs: 1</t>
+        </is>
+      </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 404 Client Error: Not Found for url: https://www.ses.com/careers</t>
-        </is>
-      </c>
-      <c r="K267" s="2" t="inlineStr"/>
+          <t>SuccessFactors career site</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
+          <t>careers.ses.com</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -12336,16 +12352,12 @@
         <v>1</v>
       </c>
       <c r="G271" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H271" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I271" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I271" s="2" t="inlineStr"/>
       <c r="J271" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12887,7 +12899,7 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F284" s="2" t="n">
         <v>0</v>
@@ -14075,7 +14087,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14255,7 +14267,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>0</v>
@@ -14591,7 +14603,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>0</v>
@@ -14636,7 +14648,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14677,25 +14689,29 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F326" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G326" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H326" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I326" s="2" t="inlineStr"/>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 2+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -14910,7 +14926,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>1</v>
@@ -15000,22 +15016,18 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I333" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 2</t>
-        </is>
-      </c>
+      <c r="I333" s="2" t="inlineStr"/>
       <c r="J333" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15049,18 +15061,22 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr"/>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
           <t>remembered</t>

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>3</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -2021,11 +2021,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>generic</t>
-        </is>
-      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>error</t>
@@ -2049,11 +2045,7 @@
           <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.aviva.co.uk/</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.aviva.co.uk/</t>
-        </is>
-      </c>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2204,22 +2196,18 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2290,7 +2278,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2888,22 +2876,18 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 4, experience: internship: 1</t>
-        </is>
-      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2974,10 +2958,10 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>1</v>
@@ -2987,7 +2971,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3023,22 +3007,18 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3078,16 +3058,12 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3121,7 +3097,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3322,7 +3298,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3584,10 +3560,10 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>0</v>
@@ -3756,22 +3732,18 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3977,7 +3949,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>2</v>
@@ -4517,18 +4489,22 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4853,7 +4829,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -4980,7 +4956,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>0</v>
@@ -5070,22 +5046,18 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 2+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5385,25 +5357,29 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5725,7 +5701,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" s="2" t="n">
         <v>0</v>
@@ -6024,7 +6000,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>0</v>
@@ -6319,29 +6295,25 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6745,22 +6717,18 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1</t>
-        </is>
-      </c>
+      <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -6839,7 +6807,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>7</v>
@@ -6966,7 +6934,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>6</v>
@@ -7056,7 +7024,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -7781,20 +7749,20 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1</t>
+          <t>experience: senior title: 1, experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -7875,7 +7843,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>0</v>
@@ -8301,7 +8269,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>2</v>
@@ -8521,7 +8489,7 @@
         <v>214</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G183" s="2" t="n">
         <v>0</v>
@@ -8600,7 +8568,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>0</v>
@@ -8682,7 +8650,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>3</v>
@@ -8772,7 +8740,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>8</v>
@@ -9362,7 +9330,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>0</v>
@@ -9407,22 +9375,18 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I204" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 3+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9890,7 +9854,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>10</v>
@@ -9972,22 +9936,18 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I217" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 2</t>
-        </is>
-      </c>
+      <c r="I217" s="2" t="inlineStr"/>
       <c r="J217" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10582,22 +10542,18 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G231" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I231" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I231" s="2" t="inlineStr"/>
       <c r="J231" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10758,7 +10714,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -10840,10 +10796,10 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G237" s="2" t="n">
         <v>1</v>
@@ -10853,7 +10809,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>experience: requires 10+ yrs: 1</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -11024,7 +10980,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>3</v>
@@ -11286,20 +11242,20 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F247" s="2" t="n">
         <v>37</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>experience: no entry-level signal: 1, experience: requires 5+ yrs: 1, experience: requires 3+ yrs: 1</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -11376,7 +11332,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E249" s="2" t="n">
@@ -11394,7 +11350,7 @@
       <c r="I249" s="2" t="inlineStr"/>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.rolls-royce.com/en</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K249" s="2" t="inlineStr">
@@ -11470,7 +11426,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11814,18 +11770,22 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I259" s="2" t="inlineStr"/>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12039,20 +11999,20 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>experience: requires 3+ yrs: 1, experience: no entry-level signal: 1, experience: requires 2+ yrs: 1</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -12170,7 +12130,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>1</v>
@@ -12183,12 +12143,12 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 6-10 yrs: 1</t>
+          <t>experience: requires 5+ yrs: 1</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K267" s="2" t="inlineStr">
@@ -12899,18 +12859,22 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 2, experience: requires 5-8 yrs: 1</t>
+        </is>
+      </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14087,7 +14051,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14173,7 +14137,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E314" s="2" t="n">
@@ -14191,7 +14155,7 @@
       <c r="I314" s="2" t="inlineStr"/>
       <c r="J314" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.veolia.com/en/careers</t>
         </is>
       </c>
       <c r="K314" s="2" t="inlineStr">
@@ -14267,7 +14231,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>0</v>
@@ -14558,7 +14522,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>0</v>
@@ -14603,7 +14567,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>0</v>
@@ -14648,7 +14612,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14689,29 +14653,25 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F326" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G326" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H326" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I326" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 2+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I326" s="2" t="inlineStr"/>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -14787,20 +14747,20 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>outside Europe: 2</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr">
@@ -14881,7 +14841,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>0</v>
@@ -14932,12 +14892,16 @@
         <v>1</v>
       </c>
       <c r="G331" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H331" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I331" s="2" t="inlineStr"/>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J331" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15019,15 +14983,19 @@
         <v>37</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I333" s="2" t="inlineStr"/>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 2, not in English: 1</t>
+        </is>
+      </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15061,22 +15029,18 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I334" s="2" t="inlineStr"/>
       <c r="J334" s="2" t="inlineStr">
         <is>
           <t>remembered</t>

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,11 @@
     </font>
     <font>
       <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,10 +66,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -142,7 +148,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Newmatches" displayName="Newmatches" ref="A1:J3" headerRowCount="1">
+  <autoFilter ref="A1:J3"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Company"/>
+    <tableColumn id="2" name="Job title"/>
+    <tableColumn id="3" name="Location"/>
+    <tableColumn id="4" name="Posted"/>
+    <tableColumn id="5" name="Experience"/>
+    <tableColumn id="6" name="HQ country"/>
+    <tableColumn id="7" name="Sector"/>
+    <tableColumn id="8" name="Link"/>
+    <tableColumn id="9" name="Found on"/>
+    <tableColumn id="10" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J3" headerRowCount="1">
+  <autoFilter ref="A1:J3"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Company"/>
+    <tableColumn id="2" name="Job title"/>
+    <tableColumn id="3" name="Location"/>
+    <tableColumn id="4" name="Posted"/>
+    <tableColumn id="5" name="Experience"/>
+    <tableColumn id="6" name="HQ country"/>
+    <tableColumn id="7" name="Sector"/>
+    <tableColumn id="8" name="Link"/>
+    <tableColumn id="9" name="Found on"/>
+    <tableColumn id="10" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
   <autoFilter ref="A1:K337"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Company"/>
@@ -450,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -517,8 +561,111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Danske Bank</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 (first seen)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>location not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BT Group</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -528,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -595,8 +742,111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Danske Bank</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 (first seen)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>location not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BT Group</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -793,7 +1043,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>RetryError: HTTPSConnectionPool(host='www.abnamro.com', port=443): Max retries exceeded with url: /en/careers (Caused by ResponseError('too many 503 error responses'))</t>
+          <t>ConnectionError: HTTPSConnectionPool(host='www.abnamro.com', port=443): Max retries exceeded with url: /en/careers (Caused by ReadTimeoutError("HTTPSConnectionPool(host='www.abn</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -902,7 +1152,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1082,10 +1332,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -1463,7 +1713,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -1680,7 +1930,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>3</v>
@@ -1942,7 +2192,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -2196,18 +2446,22 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 2</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2278,7 +2532,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2876,18 +3130,22 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 5, experience: senior level: 1</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2958,22 +3216,18 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3007,18 +3261,22 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 2</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3097,7 +3355,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3298,7 +3556,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3380,7 +3638,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3560,18 +3818,22 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3732,7 +3994,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>0</v>
@@ -3777,7 +4039,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -3900,25 +4162,25 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3949,7 +4211,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>2</v>
@@ -4170,25 +4432,29 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4489,22 +4755,18 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4956,7 +5218,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>0</v>
@@ -5046,10 +5308,10 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>0</v>
@@ -5374,7 +5636,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -5406,7 +5668,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
@@ -5424,7 +5686,7 @@
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>RetryError: HTTPSConnectionPool(host='careers.feedzai.com', port=443): Max retries exceeded with url: / (Caused by ResponseError('too many 504 error responses'))</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5701,7 +5963,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="2" t="n">
         <v>0</v>
@@ -6000,7 +6262,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>0</v>
@@ -6717,7 +6979,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>3</v>
@@ -6807,10 +7069,10 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G144" s="2" t="n">
         <v>0</v>
@@ -6934,7 +7196,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>6</v>
@@ -7024,7 +7286,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -7752,7 +8014,7 @@
         <v>306</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G166" s="2" t="n">
         <v>2</v>
@@ -7762,7 +8024,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 1, experience: no entry-level signal: 1</t>
+          <t>experience: no entry-level signal: 1, experience: senior title: 1</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -7843,7 +8105,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>0</v>
@@ -8269,18 +8531,22 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8486,7 +8752,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -8568,7 +8834,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>0</v>
@@ -8650,7 +8916,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>3</v>
@@ -8740,7 +9006,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>8</v>
@@ -9330,7 +9596,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>0</v>
@@ -9375,7 +9641,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>1</v>
@@ -9719,7 +9985,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -9854,18 +10120,22 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9936,18 +10206,22 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 2</t>
+        </is>
+      </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10542,7 +10816,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>9</v>
@@ -10632,7 +10906,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>4</v>
@@ -10796,22 +11070,18 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H237" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I237" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 10+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I237" s="2" t="inlineStr"/>
       <c r="J237" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10980,10 +11250,10 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F241" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G241" s="2" t="n">
         <v>0</v>
@@ -11245,17 +11515,17 @@
         <v>313</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1, experience: requires 5+ yrs: 1, experience: requires 3+ yrs: 1</t>
+          <t>experience: requires 2+ yrs: 1</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -11426,7 +11696,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11680,7 +11950,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>3</v>
@@ -11770,22 +12040,18 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I259" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1</t>
-        </is>
-      </c>
+      <c r="I259" s="2" t="inlineStr"/>
       <c r="J259" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11999,20 +12265,20 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 3+ yrs: 1, experience: no entry-level signal: 1, experience: requires 2+ yrs: 1</t>
+          <t>experience: requires 3+ yrs: 1</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -12130,22 +12396,18 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G267" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H267" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I267" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I267" s="2" t="inlineStr"/>
       <c r="J267" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12859,20 +13121,20 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2, experience: requires 5-8 yrs: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
@@ -14051,7 +14313,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14130,11 +14392,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C314" s="2" t="inlineStr">
-        <is>
-          <t>generic</t>
-        </is>
-      </c>
+      <c r="C314" s="2" t="inlineStr"/>
       <c r="D314" s="2" t="inlineStr">
         <is>
           <t>error</t>
@@ -14158,11 +14416,7 @@
           <t>HTTPError: 403 Client Error: Forbidden for url: https://www.veolia.com/en/careers</t>
         </is>
       </c>
-      <c r="K314" s="2" t="inlineStr">
-        <is>
-          <t>https://www.veolia.com/en/careers</t>
-        </is>
-      </c>
+      <c r="K314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -14231,7 +14485,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>0</v>
@@ -14522,7 +14776,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>0</v>
@@ -14567,18 +14821,22 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I324" s="2" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1, not in English: 1</t>
+        </is>
+      </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14612,7 +14870,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14747,10 +15005,10 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G328" s="2" t="n">
         <v>2</v>
@@ -14760,7 +15018,7 @@
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2</t>
+          <t>experience: senior title: 1, outside Europe: 1</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr">
@@ -14841,7 +15099,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>0</v>
@@ -14886,22 +15144,18 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G331" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H331" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I331" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I331" s="2" t="inlineStr"/>
       <c r="J331" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14980,20 +15234,20 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2, not in English: 1</t>
+          <t>experience: requires 5+ yrs: 1</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr">
@@ -15029,10 +15283,10 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G334" s="2" t="n">
         <v>0</v>
@@ -15070,7 +15324,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E335" s="2" t="n">
@@ -15088,7 +15342,7 @@
       <c r="I335" s="2" t="inlineStr"/>
       <c r="J335" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://orsted.com/en/careers</t>
         </is>
       </c>
       <c r="K335" s="2" t="inlineStr">

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Newmatches" displayName="Newmatches" ref="A1:J3" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Recentmatches" displayName="Recentmatches" ref="A1:J3" headerRowCount="1">
   <autoFilter ref="A1:J3"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Company"/>
@@ -167,26 +167,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J3" headerRowCount="1">
-  <autoFilter ref="A1:J3"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="Company"/>
-    <tableColumn id="2" name="Job title"/>
-    <tableColumn id="3" name="Location"/>
-    <tableColumn id="4" name="Posted"/>
-    <tableColumn id="5" name="Experience"/>
-    <tableColumn id="6" name="HQ country"/>
-    <tableColumn id="7" name="Sector"/>
-    <tableColumn id="8" name="Link"/>
-    <tableColumn id="9" name="Found on"/>
-    <tableColumn id="10" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
   <autoFilter ref="A1:K337"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Company"/>
@@ -494,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -561,111 +542,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Danske Bank</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 (first seen)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>entry-level title</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Banking</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Open job</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>location not stated</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>BT Group</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Junior Project Manager</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>entry-level title</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Telecom</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Open job</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -1043,7 +921,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>ConnectionError: HTTPSConnectionPool(host='www.abnamro.com', port=443): Max retries exceeded with url: /en/careers (Caused by ReadTimeoutError("HTTPSConnectionPool(host='www.abn</t>
+          <t>RetryError: HTTPSConnectionPool(host='www.abnamro.com', port=443): Max retries exceeded with url: /en/careers (Caused by ResponseError('too many 503 error responses'))</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -1152,18 +1030,22 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -1332,7 +1214,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>15</v>
@@ -1713,18 +1595,22 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 2</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -1930,7 +1816,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>3</v>
@@ -2192,18 +2078,22 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2446,20 +2336,20 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 2</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2532,7 +2422,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2614,7 +2504,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
@@ -3130,22 +3020,18 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>21</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 5, experience: senior level: 1</t>
-        </is>
-      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3216,7 +3102,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>7</v>
@@ -3261,20 +3147,20 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 2</t>
+          <t>experience: senior title: 1, experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3355,7 +3241,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3556,7 +3442,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3638,7 +3524,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3818,22 +3704,18 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3994,18 +3876,22 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4162,25 +4048,25 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4211,10 +4097,10 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>0</v>
@@ -4432,29 +4318,25 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4755,7 +4637,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>3</v>
@@ -5091,7 +4973,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5218,18 +5100,22 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 2</t>
+        </is>
+      </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5308,7 +5194,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>0</v>
@@ -5619,29 +5505,25 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5668,7 +5550,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
@@ -5686,7 +5568,7 @@
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>RetryError: HTTPSConnectionPool(host='careers.feedzai.com', port=443): Max retries exceeded with url: / (Caused by ResponseError('too many 504 error responses'))</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6123,25 +6005,29 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -6979,7 +6865,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>3</v>
@@ -7196,18 +7082,22 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7286,7 +7176,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -8011,22 +7901,18 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>25</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1, experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8105,7 +7991,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>0</v>
@@ -8531,10 +8417,10 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G178" s="2" t="n">
         <v>1</v>
@@ -8544,7 +8430,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>not in English: 1</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -8752,7 +8638,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -9006,7 +8892,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>8</v>
@@ -9170,7 +9056,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>1</v>
@@ -9596,7 +9482,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>0</v>
@@ -9641,7 +9527,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>1</v>
@@ -9981,11 +9867,11 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -9999,7 +9885,7 @@
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>JSONDecodeError: Expecting value: line 1 column 1 (char 0)</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -10120,22 +10006,18 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G215" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I215" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I215" s="2" t="inlineStr"/>
       <c r="J215" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10206,20 +10088,20 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2</t>
+          <t>experience: requires 5+ yrs: 1</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -10816,7 +10698,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>9</v>
@@ -10906,7 +10788,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>4</v>
@@ -11073,7 +10955,7 @@
         <v>28</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G237" s="2" t="n">
         <v>0</v>
@@ -11250,7 +11132,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11512,7 +11394,7 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F247" s="2" t="n">
         <v>34</v>
@@ -11525,7 +11407,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 2+ yrs: 1</t>
+          <t>experience: requires 5+ yrs: 1</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -11696,7 +11578,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11950,7 +11832,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>3</v>
@@ -12040,7 +11922,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>6</v>
@@ -12265,22 +12147,18 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I264" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 3+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I264" s="2" t="inlineStr"/>
       <c r="J264" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12396,7 +12274,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>1</v>
@@ -13121,22 +12999,18 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I284" s="2" t="inlineStr"/>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14313,7 +14187,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14392,10 +14266,14 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C314" s="2" t="inlineStr"/>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E314" s="2" t="n">
@@ -14413,10 +14291,14 @@
       <c r="I314" s="2" t="inlineStr"/>
       <c r="J314" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.veolia.com/en/careers</t>
-        </is>
-      </c>
-      <c r="K314" s="2" t="inlineStr"/>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.veolia.com/en/careers</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -14485,18 +14367,22 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H316" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I316" s="2" t="inlineStr"/>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14776,7 +14662,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>0</v>
@@ -14821,22 +14707,18 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I324" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1, not in English: 1</t>
-        </is>
-      </c>
+      <c r="I324" s="2" t="inlineStr"/>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14870,7 +14752,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -15005,22 +14887,18 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I328" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1, outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I328" s="2" t="inlineStr"/>
       <c r="J328" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15099,18 +14977,22 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F330" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G330" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H330" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I330" s="2" t="inlineStr"/>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J330" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15144,7 +15026,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>1</v>
@@ -15234,20 +15116,20 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F333" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G333" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G333" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 5+ yrs: 1</t>
+          <t>outside Europe: 1, experience: requires 3-5 yrs: 1</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr">
@@ -15283,7 +15165,7 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>0</v>
@@ -15324,7 +15206,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E335" s="2" t="n">
@@ -15342,7 +15224,7 @@
       <c r="I335" s="2" t="inlineStr"/>
       <c r="J335" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://orsted.com/en/careers</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K335" s="2" t="inlineStr">

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -1030,22 +1030,18 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -1595,7 +1591,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>2</v>
@@ -1608,7 +1604,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2</t>
+          <t>experience: no entry-level signal: 1, not in English: 1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2078,22 +2074,18 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2336,22 +2328,18 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2422,7 +2410,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -3020,7 +3008,7 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>21</v>
@@ -3147,22 +3135,18 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1, experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3442,7 +3426,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3704,7 +3688,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>1</v>
@@ -3876,7 +3860,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>1</v>
@@ -3889,7 +3873,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4973,7 +4957,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5100,22 +5084,18 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 2</t>
-        </is>
-      </c>
+      <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5194,18 +5174,22 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5505,25 +5489,29 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5550,25 +5538,29 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 7+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6005,29 +5997,25 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -6865,18 +6853,22 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7088,16 +7080,12 @@
         <v>7</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7176,7 +7164,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -7901,7 +7889,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>25</v>
@@ -7991,7 +7979,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>0</v>
@@ -8417,22 +8405,18 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8638,7 +8622,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -9867,11 +9851,11 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -9885,7 +9869,7 @@
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>JSONDecodeError: Expecting value: line 1 column 1 (char 0)</t>
+          <t>found via job search page</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -10088,22 +10072,18 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>35</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I217" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I217" s="2" t="inlineStr"/>
       <c r="J217" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10698,10 +10678,10 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G231" s="2" t="n">
         <v>0</v>
@@ -10870,7 +10850,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -10952,7 +10932,7 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>0</v>
@@ -11132,7 +11112,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11394,22 +11374,18 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I247" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I247" s="2" t="inlineStr"/>
       <c r="J247" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11578,7 +11554,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11832,7 +11808,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>3</v>
@@ -11922,7 +11898,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>6</v>
@@ -12147,10 +12123,10 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G264" s="2" t="n">
         <v>0</v>
@@ -12274,7 +12250,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>1</v>
@@ -12999,18 +12975,22 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14187,7 +14167,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14367,22 +14347,18 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H316" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I316" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1</t>
-        </is>
-      </c>
+      <c r="I316" s="2" t="inlineStr"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14707,7 +14683,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>1</v>
@@ -14752,7 +14728,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14887,7 +14863,7 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F328" s="2" t="n">
         <v>39</v>
@@ -14977,22 +14953,18 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G330" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H330" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I330" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I330" s="2" t="inlineStr"/>
       <c r="J330" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15116,20 +15088,20 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F333" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G333" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G333" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1, experience: requires 3-5 yrs: 1</t>
+          <t>experience: requires 4-6 yrs: 1, experience: requires 5+ yrs: 1, experience: requires 3-5 yrs: 1</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr">
@@ -15165,18 +15137,22 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr"/>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>experience: internship: 1</t>
+        </is>
+      </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
           <t>remembered</t>

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>15</v>
@@ -1591,20 +1591,20 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1, not in English: 1</t>
+          <t>experience: requires 5-8 yrs: 1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -2328,18 +2328,22 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 4</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2410,7 +2414,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2492,10 +2496,10 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>0</v>
@@ -3008,18 +3012,22 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3090,10 +3098,10 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>0</v>
@@ -3138,7 +3146,7 @@
         <v>38</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0</v>
@@ -3426,7 +3434,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3508,7 +3516,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3688,18 +3696,22 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G69" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3860,22 +3872,18 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3909,7 +3917,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -4081,7 +4089,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>1</v>
@@ -4261,7 +4269,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>0</v>
@@ -4347,25 +4355,29 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4621,7 +4633,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>3</v>
@@ -4957,7 +4969,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5084,10 +5096,10 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>0</v>
@@ -5174,10 +5186,10 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>1</v>
@@ -5187,7 +5199,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 5+ yrs: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -5489,29 +5501,25 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5538,29 +5546,25 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 7+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6136,7 +6140,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>0</v>
@@ -6853,22 +6857,18 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1</t>
-        </is>
-      </c>
+      <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>25</v>
@@ -8405,18 +8405,22 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8622,7 +8626,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -8704,7 +8708,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>0</v>
@@ -8876,10 +8880,10 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G189" s="2" t="n">
         <v>0</v>
@@ -9040,7 +9044,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>1</v>
@@ -9511,7 +9515,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>1</v>
@@ -9869,7 +9873,7 @@
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -9990,7 +9994,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>10</v>
@@ -10072,18 +10076,22 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 4</t>
+        </is>
+      </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10678,7 +10686,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>8</v>
@@ -10768,10 +10776,10 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G233" s="2" t="n">
         <v>0</v>
@@ -10850,7 +10858,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -10932,7 +10940,7 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>0</v>
@@ -11112,7 +11120,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11374,10 +11382,10 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G247" s="2" t="n">
         <v>0</v>
@@ -11554,7 +11562,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11808,7 +11816,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>3</v>
@@ -11898,7 +11906,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>6</v>
@@ -12123,7 +12131,7 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F264" s="2" t="n">
         <v>0</v>
@@ -12975,22 +12983,18 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F284" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I284" s="2" t="inlineStr"/>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14167,7 +14171,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14350,7 +14354,7 @@
         <v>48</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G316" s="2" t="n">
         <v>0</v>
@@ -14638,7 +14642,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>0</v>
@@ -14683,7 +14687,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>1</v>
@@ -14728,7 +14732,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14863,7 +14867,7 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F328" s="2" t="n">
         <v>39</v>
@@ -14953,7 +14957,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>1</v>
@@ -15088,22 +15092,18 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I333" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 4-6 yrs: 1, experience: requires 5+ yrs: 1, experience: requires 3-5 yrs: 1</t>
-        </is>
-      </c>
+      <c r="I333" s="2" t="inlineStr"/>
       <c r="J333" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G334" s="2" t="n">
         <v>1</v>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>experience: internship: 1</t>
+          <t>not in English: 1</t>
         </is>
       </c>
       <c r="J334" s="2" t="inlineStr">

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>15</v>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 5-8 yrs: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2074,18 +2074,22 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2153,10 +2157,14 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
@@ -2174,10 +2182,14 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.aviva.co.uk/</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.aviva.co.uk/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2328,20 +2340,20 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 4</t>
+          <t>experience: no entry-level signal: 2, outside Europe: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2414,7 +2426,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2496,18 +2508,22 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2731,7 +2747,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 404 Client Error: Not Found for url: https://www.blablacar.co.uk/careers</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.blablacar.com/careers</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -3012,22 +3028,18 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>22</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3098,10 +3110,10 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>0</v>
@@ -3143,10 +3155,10 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0</v>
@@ -3233,7 +3245,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3434,7 +3446,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3516,7 +3528,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3696,20 +3708,20 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>experience: requires 6+ yrs: 1, experience: requires 5+ yrs: 1, experience: senior title: 1</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -3872,7 +3884,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>0</v>
@@ -4089,7 +4101,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>1</v>
@@ -4269,7 +4281,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>0</v>
@@ -4355,29 +4367,25 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4633,18 +4641,22 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4969,7 +4981,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5096,7 +5108,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>0</v>
@@ -5186,22 +5198,18 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5235,7 +5243,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>0</v>
@@ -5546,14 +5554,14 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>0</v>
@@ -5564,7 +5572,7 @@
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6140,7 +6148,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>0</v>
@@ -6857,7 +6865,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>1</v>
@@ -6947,7 +6955,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7077,15 +7085,19 @@
         <v>106</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7889,18 +7901,22 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>25</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8405,22 +8421,18 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8626,7 +8638,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -8708,7 +8720,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>0</v>
@@ -8790,7 +8802,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>3</v>
@@ -8883,7 +8895,7 @@
         <v>32</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G189" s="2" t="n">
         <v>0</v>
@@ -9470,7 +9482,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>0</v>
@@ -9515,18 +9527,22 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F204" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G204" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H204" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 1</t>
+        </is>
+      </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9994,7 +10010,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>10</v>
@@ -10079,17 +10095,17 @@
         <v>375</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 4</t>
+          <t>experience: requires 3+ yrs: 1</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -10776,7 +10792,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>1</v>
@@ -10940,7 +10956,7 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>0</v>
@@ -11120,7 +11136,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11382,18 +11398,22 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F247" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I247" s="2" t="inlineStr"/>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 2</t>
+        </is>
+      </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11562,7 +11582,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11816,7 +11836,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>3</v>
@@ -11906,18 +11926,22 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I259" s="2" t="inlineStr"/>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12131,18 +12155,22 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I264" s="2" t="inlineStr"/>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12258,10 +12286,10 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G267" s="2" t="n">
         <v>0</v>
@@ -12553,25 +12581,29 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E274" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F274" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr">
@@ -12983,18 +13015,22 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F284" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -13190,12 +13226,16 @@
         <v>4</v>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H289" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I289" s="2" t="inlineStr"/>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14171,7 +14211,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14351,18 +14391,22 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H316" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I316" s="2" t="inlineStr"/>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14687,18 +14731,22 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I324" s="2" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14732,7 +14780,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14867,18 +14915,22 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I328" s="2" t="inlineStr"/>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 3, experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14957,7 +15009,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>1</v>
@@ -15002,7 +15054,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>1</v>
@@ -15092,10 +15144,10 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G333" s="2" t="n">
         <v>0</v>
@@ -15137,20 +15189,20 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F334" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G334" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G334" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>not in English: 1</t>
+          <t>experience: senior title: 2</t>
         </is>
       </c>
       <c r="J334" s="2" t="inlineStr">

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>15</v>
@@ -1591,20 +1591,20 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>experience: no entry-level signal: 1, experience: requires 8+ yrs: 1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>3</v>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
@@ -2182,7 +2182,7 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.aviva.co.uk/</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2340,20 +2340,20 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 2, outside Europe: 1</t>
+          <t>experience: no entry-level signal: 1, outside Europe: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2508,22 +2508,18 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2747,7 +2743,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.blablacar.com/careers</t>
+          <t>HTTPError: 404 Client Error: Not Found for url: https://www.blablacar.co.uk/careers</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -3028,18 +3024,22 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 3</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3110,18 +3110,22 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3158,7 +3162,7 @@
         <v>37</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0</v>
@@ -3245,7 +3249,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3446,7 +3450,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3528,7 +3532,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3708,22 +3712,18 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 6+ yrs: 1, experience: requires 5+ yrs: 1, experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3884,18 +3884,22 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 3+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3929,7 +3933,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -4052,25 +4056,29 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4101,18 +4109,22 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G78" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4322,25 +4334,29 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4647,16 +4663,12 @@
         <v>4</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4981,7 +4993,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5108,18 +5120,22 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5198,10 +5214,10 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>0</v>
@@ -5554,14 +5570,14 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>0</v>
@@ -5572,7 +5588,7 @@
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5849,7 +5865,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" s="2" t="n">
         <v>0</v>
@@ -6865,18 +6881,22 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 2</t>
+        </is>
+      </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -6955,7 +6975,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7082,22 +7102,18 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7901,22 +7917,18 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1</t>
-        </is>
-      </c>
+      <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7995,7 +8007,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>0</v>
@@ -8424,7 +8436,7 @@
         <v>47</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G178" s="2" t="n">
         <v>0</v>
@@ -8638,7 +8650,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -8720,7 +8732,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>0</v>
@@ -8802,7 +8814,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>3</v>
@@ -8892,18 +8904,22 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 1</t>
+        </is>
+      </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9056,7 +9072,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>1</v>
@@ -9396,30 +9412,34 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H201" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 3</t>
+        </is>
+      </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 422 Client Error: Unprocessable Entity for url: https://novozymes.wd103.myworkdayjobs.com/wday/cxs/novozymes/Novonesis_Careers/jobs</t>
+          <t>found via job search page</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>novozymes.wd103.myworkdayjobs.com|novozymes|Novonesis_Careers</t>
+          <t>novonesis.wd103.myworkdayjobs.com|novonesis|Novonesis_Careers</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9502,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>0</v>
@@ -9527,22 +9547,18 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I204" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9875,7 +9891,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -10010,7 +10026,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>10</v>
@@ -10092,7 +10108,7 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>38</v>
@@ -10105,7 +10121,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 3+ yrs: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -10702,18 +10718,22 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H231" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I231" s="2" t="inlineStr"/>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10792,7 +10812,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>1</v>
@@ -10874,7 +10894,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -10956,7 +10976,7 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>0</v>
@@ -11136,7 +11156,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11398,20 +11418,20 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -11582,7 +11602,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11836,18 +11856,22 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F257" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H257" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I257" s="2" t="inlineStr"/>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11926,20 +11950,20 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>outside Europe: 2</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
@@ -12155,10 +12179,10 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G264" s="2" t="n">
         <v>1</v>
@@ -12286,18 +12310,22 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I267" s="2" t="inlineStr"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12591,16 +12619,12 @@
         <v>1</v>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H274" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I274" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I274" s="2" t="inlineStr"/>
       <c r="J274" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -13015,22 +13039,18 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I284" s="2" t="inlineStr"/>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -13226,16 +13246,12 @@
         <v>4</v>
       </c>
       <c r="G289" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H289" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I289" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I289" s="2" t="inlineStr"/>
       <c r="J289" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14211,7 +14227,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14391,22 +14407,18 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H316" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I316" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I316" s="2" t="inlineStr"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14734,19 +14746,15 @@
         <v>39</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I324" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I324" s="2" t="inlineStr"/>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14780,7 +14788,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14915,20 +14923,20 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 3, experience: no entry-level signal: 1</t>
+          <t>experience: senior title: 2, outside Europe: 1</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr">
@@ -15009,18 +15017,22 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G330" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H330" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I330" s="2" t="inlineStr"/>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J330" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15144,7 +15156,7 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F333" s="2" t="n">
         <v>0</v>
@@ -15189,10 +15201,10 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G334" s="2" t="n">
         <v>2</v>
@@ -15202,7 +15214,7 @@
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 2</t>
+          <t>not in English: 1, outside Europe: 1</t>
         </is>
       </c>
       <c r="J334" s="2" t="inlineStr">

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>15</v>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>2</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1, experience: requires 8+ yrs: 1</t>
+          <t>not in English: 1, outside Europe: 1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>3</v>
@@ -2074,22 +2074,18 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2157,11 +2153,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>generic</t>
-        </is>
-      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>error</t>
@@ -2185,11 +2177,7 @@
           <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.aviva.co.uk/</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.aviva.co.uk/</t>
-        </is>
-      </c>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2340,20 +2328,20 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1, outside Europe: 1</t>
+          <t>experience: no entry-level signal: 4</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2426,7 +2414,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2508,7 +2496,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
@@ -3024,20 +3012,20 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 3</t>
+          <t>outside Europe: 5</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3110,22 +3098,18 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3159,18 +3143,22 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1, experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3204,10 +3192,10 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>0</v>
@@ -3249,7 +3237,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3450,7 +3438,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3532,7 +3520,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3712,10 +3700,10 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>0</v>
@@ -3884,22 +3872,18 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 3+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3933,7 +3917,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -4056,29 +4040,25 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4344,16 +4324,12 @@
         <v>1</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4657,7 +4633,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>4</v>
@@ -4993,7 +4969,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5120,7 +5096,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>1</v>
@@ -5133,7 +5109,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>not in English: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5214,7 +5190,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>0</v>
@@ -6164,18 +6140,22 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 2</t>
+        </is>
+      </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -6459,25 +6439,29 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>experience: internship: 1, experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6881,10 +6865,10 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>2</v>
@@ -7102,7 +7086,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>8</v>
@@ -7192,7 +7176,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -7917,7 +7901,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>24</v>
@@ -8007,7 +7991,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>0</v>
@@ -8436,7 +8420,7 @@
         <v>47</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G178" s="2" t="n">
         <v>0</v>
@@ -8650,7 +8634,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -8814,7 +8798,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>3</v>
@@ -8904,22 +8888,18 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I189" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9072,7 +9052,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>1</v>
@@ -9416,25 +9396,21 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G201" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I201" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 3</t>
-        </is>
-      </c>
+      <c r="I201" s="2" t="inlineStr"/>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -9547,7 +9523,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>2</v>
@@ -9891,7 +9867,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -10026,18 +10002,22 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F215" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10108,10 +10088,10 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G217" s="2" t="n">
         <v>1</v>
@@ -10121,7 +10101,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -10718,10 +10698,10 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G231" s="2" t="n">
         <v>1</v>
@@ -10731,7 +10711,7 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
@@ -10812,18 +10792,22 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F233" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G233" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G233" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H233" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 1</t>
+        </is>
+      </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10894,7 +10878,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -10976,18 +10960,22 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11156,7 +11144,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11418,10 +11406,10 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G247" s="2" t="n">
         <v>1</v>
@@ -11602,7 +11590,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11856,10 +11844,10 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F257" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G257" s="2" t="n">
         <v>1</v>
@@ -11869,7 +11857,7 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1</t>
+          <t>experience: requires 5+ yrs: 1</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
@@ -11950,20 +11938,20 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
@@ -11995,25 +11983,29 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F260" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H260" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I260" s="2" t="inlineStr"/>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 2</t>
+        </is>
+      </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -12179,22 +12171,18 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I264" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I264" s="2" t="inlineStr"/>
       <c r="J264" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12310,22 +12298,18 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G267" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H267" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I267" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I267" s="2" t="inlineStr"/>
       <c r="J267" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12990,7 +12974,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E283" s="2" t="n">
@@ -13008,7 +12992,7 @@
       <c r="I283" s="2" t="inlineStr"/>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.lifeatspotify.com/jobs</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr">
@@ -13039,7 +13023,7 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F284" s="2" t="n">
         <v>0</v>
@@ -14133,7 +14117,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E310" s="2" t="n">
@@ -14151,7 +14135,7 @@
       <c r="I310" s="2" t="inlineStr"/>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>HTTPError: 523 Server Error: &lt;none&gt; for url: https://www.umicore.com/en/careers/</t>
         </is>
       </c>
       <c r="K310" s="2" t="inlineStr">
@@ -14227,7 +14211,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14407,10 +14391,10 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G316" s="2" t="n">
         <v>0</v>
@@ -14698,7 +14682,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>0</v>
@@ -14743,7 +14727,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>0</v>
@@ -14788,7 +14772,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14923,20 +14907,20 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F328" s="2" t="n">
         <v>40</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 2, outside Europe: 1</t>
+          <t>outside Europe: 1, experience: requires 2+ yrs: 1</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr">
@@ -15017,22 +15001,18 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G330" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H330" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I330" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I330" s="2" t="inlineStr"/>
       <c r="J330" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15156,7 +15136,7 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F333" s="2" t="n">
         <v>0</v>
@@ -15201,22 +15181,18 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1, outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I334" s="2" t="inlineStr"/>
       <c r="J334" s="2" t="inlineStr">
         <is>
           <t>remembered</t>

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -148,8 +148,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Recentmatches" displayName="Recentmatches" ref="A1:J3" headerRowCount="1">
-  <autoFilter ref="A1:J3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Newmatches" displayName="Newmatches" ref="A1:J2" headerRowCount="1">
+  <autoFilter ref="A1:J2"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Company"/>
     <tableColumn id="2" name="Job title"/>
@@ -167,7 +167,26 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J4" headerRowCount="1">
+  <autoFilter ref="A1:J4"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Company"/>
+    <tableColumn id="2" name="Job title"/>
+    <tableColumn id="3" name="Location"/>
+    <tableColumn id="4" name="Posted"/>
+    <tableColumn id="5" name="Experience"/>
+    <tableColumn id="6" name="HQ country"/>
+    <tableColumn id="7" name="Sector"/>
+    <tableColumn id="8" name="Link"/>
+    <tableColumn id="9" name="Found on"/>
+    <tableColumn id="10" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
   <autoFilter ref="A1:K337"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Company"/>
@@ -475,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -542,8 +561,62 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Yara</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Associate Product Manager</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Porsgrunn, NO</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Fertilisers</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -553,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -623,18 +696,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Danske Bank</t>
+          <t>Yara</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+          <t>Associate Product Manager</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Porsgrunn, NO</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 (first seen)</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -644,12 +721,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Fertilisers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -659,71 +736,116 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>location not stated</t>
-        </is>
-      </c>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Danske Bank</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 (first seen)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>location not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>BT Group</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Junior Project Manager</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>entry-level title</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Telecom</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Open job</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1030,7 +1152,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1210,7 +1332,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>15</v>
@@ -1437,7 +1559,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>SSLError: HTTPSConnectionPool(host='careers.alcon.com', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.alcon.com', port=443): Max retries exceeded with url: / (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='careers.alcon.co</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1591,20 +1713,20 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>not in English: 1, outside Europe: 1</t>
+          <t>experience: requires 5+ yrs: 1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2074,18 +2196,22 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2328,10 +2454,10 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>4</v>
@@ -2341,7 +2467,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 4</t>
+          <t>outside Europe: 3, experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2496,7 +2622,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
@@ -3012,20 +3138,20 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 5</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3098,18 +3224,22 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3143,22 +3273,18 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1, experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3237,7 +3363,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3438,7 +3564,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3700,18 +3826,22 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1, experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3872,18 +4002,22 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3917,7 +4051,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -4089,22 +4223,18 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4273,7 +4403,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>0</v>
@@ -4318,18 +4448,22 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4359,25 +4493,29 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 4+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4969,7 +5107,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5096,22 +5234,18 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5190,7 +5324,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>0</v>
@@ -5546,25 +5680,29 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6146,16 +6284,12 @@
         <v>2</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 2</t>
-        </is>
-      </c>
+      <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -6439,29 +6573,25 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>experience: internship: 1, experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6865,20 +6995,20 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>not in English: 2</t>
+          <t>not in English: 1</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -6959,7 +7089,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7901,18 +8031,22 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>24</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7991,7 +8125,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>0</v>
@@ -8417,7 +8551,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>3</v>
@@ -8634,7 +8768,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -8716,18 +8850,22 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F185" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H185" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 2</t>
+        </is>
+      </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8798,18 +8936,22 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9052,7 +9194,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>1</v>
@@ -9396,7 +9538,7 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>3</v>
@@ -9478,7 +9620,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>0</v>
@@ -9523,7 +9665,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>2</v>
@@ -9867,7 +10009,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -10002,22 +10144,18 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>11</v>
       </c>
       <c r="G215" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I215" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I215" s="2" t="inlineStr"/>
       <c r="J215" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10088,20 +10226,20 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 1</t>
+          <t>outside Europe: 2</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -10698,22 +10836,18 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G231" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I231" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I231" s="2" t="inlineStr"/>
       <c r="J231" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10792,22 +10926,18 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G233" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I233" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I233" s="2" t="inlineStr"/>
       <c r="J233" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10878,7 +11008,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -10960,10 +11090,10 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G237" s="2" t="n">
         <v>1</v>
@@ -10973,7 +11103,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -11144,7 +11274,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11409,7 +11539,7 @@
         <v>306</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G247" s="2" t="n">
         <v>1</v>
@@ -11590,7 +11720,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11844,22 +11974,18 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G257" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H257" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I257" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I257" s="2" t="inlineStr"/>
       <c r="J257" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11938,22 +12064,18 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I259" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I259" s="2" t="inlineStr"/>
       <c r="J259" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11987,20 +12109,20 @@
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F260" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G260" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H260" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 2</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr">
@@ -12171,18 +12293,22 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I264" s="2" t="inlineStr"/>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1, experience: requires 5+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12298,10 +12424,10 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G267" s="2" t="n">
         <v>0</v>
@@ -12974,7 +13100,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E283" s="2" t="n">
@@ -12992,7 +13118,7 @@
       <c r="I283" s="2" t="inlineStr"/>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.lifeatspotify.com/jobs</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr">
@@ -13023,18 +13149,22 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 7+ yrs: 2, experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14117,7 +14247,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E310" s="2" t="n">
@@ -14135,7 +14265,7 @@
       <c r="I310" s="2" t="inlineStr"/>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 523 Server Error: &lt;none&gt; for url: https://www.umicore.com/en/careers/</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K310" s="2" t="inlineStr">
@@ -14211,7 +14341,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14391,18 +14521,22 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H316" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I316" s="2" t="inlineStr"/>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 2+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14682,7 +14816,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>0</v>
@@ -14727,18 +14861,22 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I324" s="2" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14772,7 +14910,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14907,22 +15045,18 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F328" s="2" t="n">
         <v>40</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I328" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1, experience: requires 2+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I328" s="2" t="inlineStr"/>
       <c r="J328" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15001,7 +15135,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>1</v>
@@ -15052,10 +15186,10 @@
         <v>1</v>
       </c>
       <c r="G331" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H331" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I331" s="2" t="inlineStr"/>
       <c r="J331" s="2" t="inlineStr">
@@ -15136,18 +15270,22 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I333" s="2" t="inlineStr"/>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1, outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15181,18 +15319,22 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr"/>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
           <t>remembered</t>

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -148,8 +148,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Newmatches" displayName="Newmatches" ref="A1:J2" headerRowCount="1">
-  <autoFilter ref="A1:J2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Recentmatches" displayName="Recentmatches" ref="A1:J4" headerRowCount="1">
+  <autoFilter ref="A1:J4"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Company"/>
     <tableColumn id="2" name="Job title"/>
@@ -167,26 +167,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J4" headerRowCount="1">
-  <autoFilter ref="A1:J4"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="Company"/>
-    <tableColumn id="2" name="Job title"/>
-    <tableColumn id="3" name="Location"/>
-    <tableColumn id="4" name="Posted"/>
-    <tableColumn id="5" name="Experience"/>
-    <tableColumn id="6" name="HQ country"/>
-    <tableColumn id="7" name="Sector"/>
-    <tableColumn id="8" name="Link"/>
-    <tableColumn id="9" name="Found on"/>
-    <tableColumn id="10" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
   <autoFilter ref="A1:K337"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Company"/>
@@ -494,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -561,62 +542,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Yara</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Associate Product Manager</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Porsgrunn, NO</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>entry-level title</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Fertilisers</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Open job</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -940,10 +867,14 @@
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -961,10 +892,14 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 404 Client Error: Not Found for url: https://www.ab-inbev.com/careers</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ab-inbev.com/careers</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1043,7 +978,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>RetryError: HTTPSConnectionPool(host='www.abnamro.com', port=443): Max retries exceeded with url: /en/careers (Caused by ResponseError('too many 503 error responses'))</t>
+          <t>ConnectionError: HTTPSConnectionPool(host='www.abnamro.com', port=443): Max retries exceeded with url: /en/careers (Caused by ReadTimeoutError("HTTPSConnectionPool(host='www.abn</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -1152,7 +1087,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1332,7 +1267,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>15</v>
@@ -1559,7 +1494,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.alcon.com', port=443): Max retries exceeded with url: / (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='careers.alcon.co</t>
+          <t>SSLError: HTTPSConnectionPool(host='careers.alcon.com', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1713,22 +1648,18 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -1934,10 +1865,10 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -1975,25 +1906,29 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2196,22 +2131,18 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2457,17 +2388,17 @@
         <v>304</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 3, experience: no entry-level signal: 1</t>
+          <t>outside Europe: 2, experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2540,7 +2471,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -3044,25 +2975,29 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3138,22 +3073,18 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3224,22 +3155,18 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3273,7 +3200,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>1</v>
@@ -3318,18 +3245,22 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3564,7 +3495,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3646,7 +3577,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3826,22 +3757,18 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1, experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4002,22 +3929,18 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4051,7 +3974,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -4223,10 +4146,10 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>0</v>
@@ -4454,16 +4377,12 @@
         <v>2</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4493,29 +4412,25 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 4+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4771,7 +4686,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>4</v>
@@ -5234,18 +5149,22 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5324,18 +5243,22 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5680,29 +5603,25 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6995,22 +6914,18 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1</t>
-        </is>
-      </c>
+      <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7089,7 +7004,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7216,10 +7131,10 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G147" s="2" t="n">
         <v>0</v>
@@ -7306,7 +7221,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -8031,22 +7946,18 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>24</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8125,18 +8036,22 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8551,7 +8466,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>3</v>
@@ -8768,7 +8683,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -8850,22 +8765,18 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G185" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I185" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 2</t>
-        </is>
-      </c>
+      <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8936,20 +8847,20 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F187" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H187" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 1</t>
+          <t>experience: senior title: 1, experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -9030,10 +8941,10 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G189" s="2" t="n">
         <v>0</v>
@@ -9194,7 +9105,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>1</v>
@@ -9538,7 +9449,7 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>3</v>
@@ -9620,7 +9531,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>0</v>
@@ -9665,7 +9576,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>2</v>
@@ -10009,7 +9920,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -10144,7 +10055,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>11</v>
@@ -10226,20 +10137,20 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2</t>
+          <t>experience: requires 2+ yrs: 1, experience: senior title: 1, experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -10836,7 +10747,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>10</v>
@@ -10926,10 +10837,10 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G233" s="2" t="n">
         <v>0</v>
@@ -11008,7 +10919,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -11093,19 +11004,15 @@
         <v>31</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H237" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I237" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I237" s="2" t="inlineStr"/>
       <c r="J237" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11442,7 +11349,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E245" s="2" t="n">
@@ -11460,7 +11367,7 @@
       <c r="I245" s="2" t="inlineStr"/>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>RetryError: HTTPSConnectionPool(host='careers.rimac-group.com', port=443): Max retries exceeded with url: / (Caused by ResponseError('too many 500 error responses'))</t>
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr">
@@ -11536,10 +11443,10 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G247" s="2" t="n">
         <v>1</v>
@@ -11720,7 +11627,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11974,10 +11881,10 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F257" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G257" s="2" t="n">
         <v>0</v>
@@ -12064,7 +11971,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>5</v>
@@ -12105,29 +12012,25 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F260" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G260" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H260" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I260" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I260" s="2" t="inlineStr"/>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -12293,20 +12196,20 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F264" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1, experience: requires 5+ yrs: 1</t>
+          <t>experience: requires 3+ yrs: 1</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -12424,18 +12327,22 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I267" s="2" t="inlineStr"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -13149,20 +13056,20 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 7+ yrs: 2, experience: senior title: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
@@ -14341,7 +14248,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14521,22 +14428,18 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H316" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I316" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 2+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I316" s="2" t="inlineStr"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14861,22 +14764,18 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I324" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I324" s="2" t="inlineStr"/>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14910,7 +14809,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -15048,15 +14947,19 @@
         <v>312</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I328" s="2" t="inlineStr"/>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15135,7 +15038,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>1</v>
@@ -15186,10 +15089,10 @@
         <v>1</v>
       </c>
       <c r="G331" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H331" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I331" s="2" t="inlineStr"/>
       <c r="J331" s="2" t="inlineStr">
@@ -15270,20 +15173,20 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F333" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 5+ yrs: 1, outside Europe: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr">
@@ -15319,22 +15222,18 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I334" s="2" t="inlineStr"/>
       <c r="J334" s="2" t="inlineStr">
         <is>
           <t>remembered</t>

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -1083,11 +1083,11 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.adidas-group.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>15</v>
@@ -1644,11 +1644,11 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -1662,7 +1662,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t xml:space="preserve">ConnectTimeout: HTTPSConnectionPool(host='jobsearch.alstom.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1906,29 +1906,25 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2127,11 +2123,11 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -2145,7 +2141,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t xml:space="preserve">ConnectTimeout: HTTPSConnectionPool(host='www.jobs.atlascopcogroup.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2391,16 +2387,12 @@
         <v>18</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 2, experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2467,11 +2459,11 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2485,7 +2477,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='basf.jobs', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by ConnectT</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2985,16 +2977,12 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3073,7 +3061,7 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>20</v>
@@ -3155,7 +3143,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>4</v>
@@ -3200,7 +3188,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>1</v>
@@ -3251,16 +3239,12 @@
         <v>6</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3294,7 +3278,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -3491,11 +3475,11 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3509,7 +3493,7 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.carlsberg.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3753,14 +3737,14 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>0</v>
@@ -3771,7 +3755,7 @@
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.coloplast.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3925,11 +3909,11 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>0</v>
@@ -3943,7 +3927,7 @@
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.crh.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Conne</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4686,7 +4670,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>4</v>
@@ -5018,11 +5002,11 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5036,7 +5020,7 @@
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.edp.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Conne</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -5149,7 +5133,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>1</v>
@@ -5162,7 +5146,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 5+ yrs: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5239,29 +5223,25 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t xml:space="preserve">ConnectTimeout: HTTPSConnectionPool(host='www.careerprofile.epiroc.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) </t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -6914,7 +6894,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>5</v>
@@ -7217,11 +7197,11 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -7235,7 +7215,7 @@
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='www.jaguarlandrovercareers.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7946,7 +7926,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>24</v>
@@ -8042,16 +8022,12 @@
         <v>1</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8462,14 +8438,14 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G178" s="2" t="n">
         <v>0</v>
@@ -8480,7 +8456,7 @@
       <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.mapfre.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Co</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -8853,16 +8829,12 @@
         <v>5</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I187" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1, experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10137,22 +10109,18 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>42</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I217" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 2+ yrs: 1, experience: senior title: 1, experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I217" s="2" t="inlineStr"/>
       <c r="J217" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10997,11 +10965,11 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>0</v>
@@ -11015,7 +10983,7 @@
       <c r="I237" s="2" t="inlineStr"/>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.reckitt.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused b</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -11349,7 +11317,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E245" s="2" t="n">
@@ -11367,7 +11335,7 @@
       <c r="I245" s="2" t="inlineStr"/>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>RetryError: HTTPSConnectionPool(host='careers.rimac-group.com', port=443): Max retries exceeded with url: / (Caused by ResponseError('too many 500 error responses'))</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr">
@@ -11449,16 +11417,12 @@
         <v>30</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I247" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I247" s="2" t="inlineStr"/>
       <c r="J247" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11627,7 +11591,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11881,7 +11845,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>4</v>
@@ -12192,29 +12156,25 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I264" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 3+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I264" s="2" t="inlineStr"/>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t xml:space="preserve">ConnectTimeout: HTTPSConnectionPool(host='job.schindler.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by </t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
@@ -12323,29 +12283,25 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G267" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H267" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I267" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I267" s="2" t="inlineStr"/>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.ses.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Co</t>
         </is>
       </c>
       <c r="K267" s="2" t="inlineStr">
@@ -13059,19 +13015,15 @@
         <v>34</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I284" s="2" t="inlineStr"/>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14248,7 +14200,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14424,11 +14376,11 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>0</v>
@@ -14442,7 +14394,7 @@
       <c r="I316" s="2" t="inlineStr"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.vestas.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by</t>
         </is>
       </c>
       <c r="K316" s="2" t="inlineStr">
@@ -14715,11 +14667,11 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>0</v>
@@ -14733,7 +14685,7 @@
       <c r="I323" s="2" t="inlineStr"/>
       <c r="J323" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.volvocars.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by</t>
         </is>
       </c>
       <c r="K323" s="2" t="inlineStr">
@@ -14764,10 +14716,10 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G324" s="2" t="n">
         <v>0</v>
@@ -14805,11 +14757,11 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14823,7 +14775,7 @@
       <c r="I325" s="2" t="inlineStr"/>
       <c r="J325" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.vonovia.de', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Co</t>
         </is>
       </c>
       <c r="K325" s="2" t="inlineStr">
@@ -14950,16 +14902,12 @@
         <v>39</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I328" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I328" s="2" t="inlineStr"/>
       <c r="J328" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15034,14 +14982,14 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F330" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G330" s="2" t="n">
         <v>0</v>
@@ -15052,7 +15000,7 @@
       <c r="I330" s="2" t="inlineStr"/>
       <c r="J330" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t xml:space="preserve">ConnectTimeout: HTTPSConnectionPool(host='careers.wartsila.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused </t>
         </is>
       </c>
       <c r="K330" s="2" t="inlineStr">
@@ -15079,14 +15027,14 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F331" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G331" s="2" t="n">
         <v>0</v>
@@ -15097,7 +15045,7 @@
       <c r="I331" s="2" t="inlineStr"/>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.yara.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Conn</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">
@@ -15169,29 +15117,25 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I333" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I333" s="2" t="inlineStr"/>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.zf.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Connec</t>
         </is>
       </c>
       <c r="K333" s="2" t="inlineStr">
@@ -15222,18 +15166,22 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr"/>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
           <t>remembered</t>

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -978,7 +978,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>ConnectionError: HTTPSConnectionPool(host='www.abnamro.com', port=443): Max retries exceeded with url: /en/careers (Caused by ReadTimeoutError("HTTPSConnectionPool(host='www.abn</t>
+          <t>RetryError: HTTPSConnectionPool(host='www.abnamro.com', port=443): Max retries exceeded with url: /en/careers (Caused by ResponseError('too many 503 error responses'))</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -1083,11 +1083,11 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.adidas-group.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1267,18 +1267,22 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>15</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -1644,25 +1648,29 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1, experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ConnectTimeout: HTTPSConnectionPool(host='jobsearch.alstom.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused </t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1865,7 +1873,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>2</v>
@@ -2123,25 +2131,29 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ConnectTimeout: HTTPSConnectionPool(host='www.jobs.atlascopcogroup.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) </t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2381,18 +2393,22 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2459,11 +2475,11 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2477,7 +2493,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='basf.jobs', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by ConnectT</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2545,7 +2561,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
@@ -2967,14 +2983,14 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>0</v>
@@ -2985,7 +3001,7 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3061,18 +3077,22 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 2</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3143,7 +3163,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>4</v>
@@ -3188,18 +3208,22 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3278,18 +3302,22 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3475,11 +3503,11 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3493,7 +3521,7 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.carlsberg.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3561,7 +3589,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3737,14 +3765,14 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>0</v>
@@ -3755,7 +3783,7 @@
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.coloplast.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3909,25 +3937,29 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1, experience: requires 15+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.crh.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Conne</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4081,25 +4113,29 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4130,7 +4166,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>3</v>
@@ -4310,7 +4346,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>0</v>
@@ -4355,10 +4391,10 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>0</v>
@@ -4396,25 +4432,29 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4670,10 +4710,10 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>0</v>
@@ -5002,11 +5042,11 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5020,7 +5060,7 @@
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.edp.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Conne</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -5133,10 +5173,10 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>1</v>
@@ -5146,7 +5186,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1</t>
+          <t>not in English: 1</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5223,25 +5263,29 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ConnectTimeout: HTTPSConnectionPool(host='www.careerprofile.epiroc.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) </t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5583,14 +5627,14 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>0</v>
@@ -5601,7 +5645,7 @@
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6894,18 +6938,22 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 2, outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -6984,7 +7032,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7197,11 +7245,11 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -7215,7 +7263,7 @@
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='www.jaguarlandrovercareers.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7926,7 +7974,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>24</v>
@@ -8016,7 +8064,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>1</v>
@@ -8438,14 +8486,14 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G178" s="2" t="n">
         <v>0</v>
@@ -8456,7 +8504,7 @@
       <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.mapfre.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Co</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -8659,7 +8707,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -8741,7 +8789,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>2</v>
@@ -8823,7 +8871,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>5</v>
@@ -8913,7 +8961,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>3</v>
@@ -9548,7 +9596,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>2</v>
@@ -9798,7 +9846,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E210" s="2" t="n">
@@ -9816,7 +9864,7 @@
       <c r="I210" s="2" t="inlineStr"/>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>ConnectionError: HTTPSConnectionPool(host='www.orlen.pl', port=443): Max retries exceeded with url: /en/career (Caused by ReadTimeoutError("HTTPSConnectionPool(host='www.orlen.p</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
@@ -10027,7 +10075,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>11</v>
@@ -10109,18 +10157,22 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 3</t>
+        </is>
+      </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -10715,7 +10767,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>10</v>
@@ -10887,7 +10939,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -10965,11 +11017,11 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>0</v>
@@ -10983,7 +11035,7 @@
       <c r="I237" s="2" t="inlineStr"/>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.reckitt.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused b</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -11411,10 +11463,10 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G247" s="2" t="n">
         <v>0</v>
@@ -11845,7 +11897,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>4</v>
@@ -11935,7 +11987,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>5</v>
@@ -12156,25 +12208,29 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I264" s="2" t="inlineStr"/>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ConnectTimeout: HTTPSConnectionPool(host='job.schindler.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by </t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
@@ -12283,14 +12339,14 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" s="2" t="n">
         <v>0</v>
@@ -12301,7 +12357,7 @@
       <c r="I267" s="2" t="inlineStr"/>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.ses.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Co</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K267" s="2" t="inlineStr">
@@ -13012,18 +13068,22 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14200,7 +14260,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14376,11 +14436,11 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>0</v>
@@ -14394,7 +14454,7 @@
       <c r="I316" s="2" t="inlineStr"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.vestas.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K316" s="2" t="inlineStr">
@@ -14667,11 +14727,11 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>0</v>
@@ -14685,7 +14745,7 @@
       <c r="I323" s="2" t="inlineStr"/>
       <c r="J323" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.volvocars.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K323" s="2" t="inlineStr">
@@ -14716,18 +14776,22 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I324" s="2" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 10+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14757,11 +14821,11 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14775,7 +14839,7 @@
       <c r="I325" s="2" t="inlineStr"/>
       <c r="J325" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.vonovia.de', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Co</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K325" s="2" t="inlineStr">
@@ -14896,18 +14960,22 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I328" s="2" t="inlineStr"/>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1, experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14982,14 +15050,14 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F330" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G330" s="2" t="n">
         <v>0</v>
@@ -15000,7 +15068,7 @@
       <c r="I330" s="2" t="inlineStr"/>
       <c r="J330" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ConnectTimeout: HTTPSConnectionPool(host='careers.wartsila.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused </t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K330" s="2" t="inlineStr">
@@ -15027,14 +15095,14 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F331" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G331" s="2" t="n">
         <v>0</v>
@@ -15045,7 +15113,7 @@
       <c r="I331" s="2" t="inlineStr"/>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.yara.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Conn</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">
@@ -15117,25 +15185,29 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I333" s="2" t="inlineStr"/>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='jobs.zf.com', port=443): Max retries exceeded with url: /services/rss/job/?locale=en_US&amp;keywords=(project%20manager) (Caused by Connec</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K333" s="2" t="inlineStr">
@@ -15166,22 +15238,18 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I334" s="2" t="inlineStr"/>
       <c r="J334" s="2" t="inlineStr">
         <is>
           <t>remembered</t>

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -148,8 +148,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Recentmatches" displayName="Recentmatches" ref="A1:J4" headerRowCount="1">
-  <autoFilter ref="A1:J4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Newmatches" displayName="Newmatches" ref="A1:J2" headerRowCount="1">
+  <autoFilter ref="A1:J2"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Company"/>
     <tableColumn id="2" name="Job title"/>
@@ -167,7 +167,26 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J5" headerRowCount="1">
+  <autoFilter ref="A1:J5"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Company"/>
+    <tableColumn id="2" name="Job title"/>
+    <tableColumn id="3" name="Location"/>
+    <tableColumn id="4" name="Posted"/>
+    <tableColumn id="5" name="Experience"/>
+    <tableColumn id="6" name="HQ country"/>
+    <tableColumn id="7" name="Sector"/>
+    <tableColumn id="8" name="Link"/>
+    <tableColumn id="9" name="Found on"/>
+    <tableColumn id="10" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
   <autoFilter ref="A1:K337"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Company"/>
@@ -475,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -542,8 +561,62 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Customer Project Officer (a)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Madrid; Spain</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>entry-level wording</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Health technology</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -553,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -623,37 +696,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Yara</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Associate Product Manager</t>
+          <t>Customer Project Officer (a)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Porsgrunn, NO</t>
+          <t>Madrid; Spain</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>entry-level title</t>
+          <t>entry-level wording</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Fertilisers</t>
+          <t>Health technology</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -663,7 +736,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -671,18 +744,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Danske Bank</t>
+          <t>Yara</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
+          <t>Associate Product Manager</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Porsgrunn, NO</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 (first seen)</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -692,12 +769,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Fertilisers</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -707,72 +784,117 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>location not stated</t>
-        </is>
-      </c>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Danske Bank</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 (first seen)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>location not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>BT Group</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Junior Project Manager</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>entry-level title</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Telecom</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Open job</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1087,7 +1209,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1101,7 +1223,7 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1267,10 +1389,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1</v>
@@ -1285,7 +1407,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1652,25 +1774,25 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1, experience: no entry-level signal: 1</t>
+          <t>experience: requires 3+ yrs: 1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1873,7 +1995,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>2</v>
@@ -1887,7 +2009,7 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2135,7 +2257,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
@@ -2148,12 +2270,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2218,10 +2340,14 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
@@ -2239,10 +2365,14 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.aviva.co.uk/</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.aviva.co.uk/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2393,25 +2523,25 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>experience: no entry-level signal: 2, outside Europe: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2479,21 +2609,25 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2534,7 +2668,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.bayer.com/en/career</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.bayer.com/en/career/</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
@@ -2561,7 +2695,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
@@ -2575,7 +2709,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2796,7 +2930,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 404 Client Error: Not Found for url: https://www.blablacar.co.uk/careers</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.blablacar.com/careers</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -3077,25 +3211,21 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>21</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 2</t>
-        </is>
-      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3163,7 +3293,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>4</v>
@@ -3177,7 +3307,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3208,25 +3338,21 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3248,7 +3374,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>recruitee</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3257,26 +3383,30 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 1, experience: mid level: 1</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>https://careers.bunq.com/</t>
+          <t>bunq</t>
         </is>
       </c>
     </row>
@@ -3302,25 +3432,21 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3507,7 +3633,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3521,7 +3647,7 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3589,7 +3715,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3603,7 +3729,7 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found via job search page</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3769,7 +3895,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>2</v>
@@ -3783,7 +3909,7 @@
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3941,25 +4067,21 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1, experience: requires 15+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3990,7 +4112,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -4004,7 +4126,7 @@
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4113,29 +4235,25 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4180,7 +4298,7 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4360,7 +4478,7 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4405,7 +4523,7 @@
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>no job platform detected; reading page directly</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4432,29 +4550,25 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4679,7 +4793,7 @@
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>no job platform detected; reading page directly</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4710,10 +4824,10 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>0</v>
@@ -4724,7 +4838,7 @@
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5046,7 +5160,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5060,7 +5174,7 @@
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -5173,25 +5287,21 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1</t>
-        </is>
-      </c>
+      <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5267,25 +5377,21 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5316,7 +5422,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>0</v>
@@ -5330,7 +5436,7 @@
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5631,10 +5737,10 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>0</v>
@@ -5936,7 +6042,7 @@
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -6221,10 +6327,10 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>0</v>
@@ -6235,7 +6341,7 @@
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6938,25 +7044,25 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>not in English: 2, outside Europe: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -7032,7 +7138,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7046,7 +7152,7 @@
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7159,7 +7265,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>7</v>
@@ -7173,7 +7279,7 @@
       <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7249,7 +7355,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -7263,7 +7369,7 @@
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7974,10 +8080,10 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G166" s="2" t="n">
         <v>0</v>
@@ -7988,7 +8094,7 @@
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found via job search page</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -8064,7 +8170,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>1</v>
@@ -8078,7 +8184,7 @@
       <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -8242,7 +8348,7 @@
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>no job platform detected; reading page directly</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -8490,7 +8596,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>1</v>
@@ -8504,7 +8610,7 @@
       <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -8606,14 +8712,10 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>generic</t>
-        </is>
-      </c>
+      <c r="C181" s="2" t="inlineStr"/>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E181" s="2" t="n">
@@ -8631,14 +8733,10 @@
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
-        </is>
-      </c>
-      <c r="K181" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.emdgroup.com/us/en</t>
-        </is>
-      </c>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.merckgroup.com/en/careers.html</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -8721,7 +8819,7 @@
       <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8803,7 +8901,7 @@
       <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found via job search page</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8871,7 +8969,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>5</v>
@@ -8885,7 +8983,7 @@
       <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -8907,16 +9005,16 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F188" s="2" t="n">
         <v>0</v>
@@ -8930,12 +9028,12 @@
       <c r="I188" s="2" t="inlineStr"/>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>nextinsurancemresandbox</t>
+          <t>https://careers.munichre.com/en/munichre</t>
         </is>
       </c>
     </row>
@@ -8975,7 +9073,7 @@
       <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -8995,14 +9093,10 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>generic</t>
-        </is>
-      </c>
+      <c r="C190" s="2" t="inlineStr"/>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E190" s="2" t="n">
@@ -9020,14 +9114,10 @@
       <c r="I190" s="2" t="inlineStr"/>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
-        </is>
-      </c>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nationalgrid.com/careers</t>
-        </is>
-      </c>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.nationalgrid.com/careers</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -9139,7 +9229,7 @@
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -9266,7 +9356,7 @@
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>no job platform detected; reading page directly</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -9469,18 +9559,22 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H201" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9551,7 +9645,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>0</v>
@@ -9565,7 +9659,7 @@
       <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found via job search page</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -9596,7 +9690,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>2</v>
@@ -9610,7 +9704,7 @@
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -9846,7 +9940,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E210" s="2" t="n">
@@ -9864,7 +9958,7 @@
       <c r="I210" s="2" t="inlineStr"/>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>ConnectionError: HTTPSConnectionPool(host='www.orlen.pl', port=443): Max retries exceeded with url: /en/career (Caused by ReadTimeoutError("HTTPSConnectionPool(host='www.orlen.p</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
@@ -9940,7 +10034,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -10075,7 +10169,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>11</v>
@@ -10089,7 +10183,7 @@
       <c r="I215" s="2" t="inlineStr"/>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -10157,25 +10251,25 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 3</t>
+          <t>outside Europe: 2, experience: senior title: 1</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found via job search page</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -10767,7 +10861,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>10</v>
@@ -10781,7 +10875,7 @@
       <c r="I231" s="2" t="inlineStr"/>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found via job search page</t>
         </is>
       </c>
       <c r="K231" s="2" t="inlineStr">
@@ -10848,7 +10942,7 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -10857,21 +10951,25 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H233" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 2, experience: requires 3-4 yrs: 1</t>
+        </is>
+      </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -10953,7 +11051,7 @@
       <c r="I235" s="2" t="inlineStr"/>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr">
@@ -11021,21 +11119,25 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -11201,7 +11303,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11215,7 +11317,7 @@
       <c r="I241" s="2" t="inlineStr"/>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -11463,21 +11565,25 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I247" s="2" t="inlineStr"/>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1, experience: no entry-level signal: 1, experience: requires 5-7 yrs: 1, experience: requires 5+ yrs: 1, experience: senior title: 1, experience: requires 8+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found via job search page</t>
         </is>
       </c>
       <c r="K247" s="2" t="inlineStr">
@@ -11643,7 +11749,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11657,7 +11763,7 @@
       <c r="I251" s="2" t="inlineStr"/>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K251" s="2" t="inlineStr">
@@ -11911,7 +12017,7 @@
       <c r="I257" s="2" t="inlineStr"/>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr">
@@ -11987,7 +12093,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>5</v>
@@ -12001,7 +12107,7 @@
       <c r="I259" s="2" t="inlineStr"/>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
@@ -12212,25 +12318,21 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I264" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I264" s="2" t="inlineStr"/>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
@@ -12343,7 +12445,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>1</v>
@@ -12357,7 +12459,7 @@
       <c r="I267" s="2" t="inlineStr"/>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K267" s="2" t="inlineStr">
@@ -12529,7 +12631,7 @@
       <c r="I271" s="2" t="inlineStr"/>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>no job platform detected; reading page directly</t>
         </is>
       </c>
       <c r="K271" s="2" t="inlineStr">
@@ -12633,7 +12735,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>workable</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -12642,26 +12744,30 @@
         </is>
       </c>
       <c r="E274" s="2" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="F274" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 1</t>
+        </is>
+      </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
-          <t>https://www.skeletontech.com/careers</t>
+          <t>skeletontech</t>
         </is>
       </c>
     </row>
@@ -13068,25 +13174,21 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I284" s="2" t="inlineStr"/>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr">
@@ -13287,7 +13389,7 @@
       <c r="I289" s="2" t="inlineStr"/>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>no job platform detected; reading page directly</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr">
@@ -13863,26 +13965,30 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F303" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G303" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H303" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I303" s="2" t="inlineStr"/>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 3, outside Europe: 2</t>
+        </is>
+      </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found via job search page</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr">
         <is>
-          <t>steeleurope.wd3.myworkdayjobs.com|steeleurope|Job_Board</t>
+          <t>thyssenkruppmaterialsna.wd12.myworkdayjobs.com|thyssenkruppmaterialsna|1</t>
         </is>
       </c>
     </row>
@@ -14260,7 +14366,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14274,7 +14380,7 @@
       <c r="I312" s="2" t="inlineStr"/>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K312" s="2" t="inlineStr">
@@ -14440,21 +14546,25 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H316" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I316" s="2" t="inlineStr"/>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K316" s="2" t="inlineStr">
@@ -14731,7 +14841,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>0</v>
@@ -14745,7 +14855,7 @@
       <c r="I323" s="2" t="inlineStr"/>
       <c r="J323" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K323" s="2" t="inlineStr">
@@ -14776,10 +14886,10 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G324" s="2" t="n">
         <v>1</v>
@@ -14794,7 +14904,7 @@
       </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K324" s="2" t="inlineStr">
@@ -14825,7 +14935,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14839,7 +14949,7 @@
       <c r="I325" s="2" t="inlineStr"/>
       <c r="J325" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K325" s="2" t="inlineStr">
@@ -14866,25 +14976,29 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F326" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G326" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H326" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I326" s="2" t="inlineStr"/>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 1</t>
+        </is>
+      </c>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>no job platform detected; reading page directly</t>
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -14960,25 +15074,21 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I328" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1, experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I328" s="2" t="inlineStr"/>
       <c r="J328" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>found on careers page</t>
         </is>
       </c>
       <c r="K328" s="2" t="inlineStr">
@@ -15054,7 +15164,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>1</v>
@@ -15068,7 +15178,7 @@
       <c r="I330" s="2" t="inlineStr"/>
       <c r="J330" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K330" s="2" t="inlineStr">
@@ -15099,7 +15209,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>2</v>
@@ -15113,7 +15223,7 @@
       <c r="I331" s="2" t="inlineStr"/>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">
@@ -15189,25 +15299,25 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F333" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G333" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G333" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 1</t>
+          <t>experience: requires 4-6 yrs: 1, experience: requires 6+ yrs: 1</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K333" s="2" t="inlineStr">
@@ -15238,21 +15348,25 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr"/>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1, experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>SuccessFactors career site</t>
         </is>
       </c>
       <c r="K334" s="2" t="inlineStr">

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -167,8 +167,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J5" headerRowCount="1">
-  <autoFilter ref="A1:J5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J6" headerRowCount="1">
+  <autoFilter ref="A1:J6"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Company"/>
     <tableColumn id="2" name="Job title"/>
@@ -564,37 +564,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Customer Project Officer (a)</t>
+          <t>Graduate Project Manager</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Madrid; Spain</t>
+          <t>GB - Edinburgh; United Kingdom</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>entry-level wording</t>
+          <t>entry-level title</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Health technology</t>
+          <t>Aerospace &amp; defence</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -696,37 +696,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Customer Project Officer (a)</t>
+          <t>Graduate Project Manager</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Madrid; Spain</t>
+          <t>GB - Edinburgh; United Kingdom</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>entry-level wording</t>
+          <t>entry-level title</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Health technology</t>
+          <t>Aerospace &amp; defence</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -744,37 +744,37 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Yara</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Associate Product Manager</t>
+          <t>Customer Project Officer (a)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Porsgrunn, NO</t>
+          <t>Madrid; Spain</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>entry-level title</t>
+          <t>entry-level wording</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Fertilisers</t>
+          <t>Health technology</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -792,18 +792,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Danske Bank</t>
+          <t>Yara</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
+          <t>Associate Product Manager</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Porsgrunn, NO</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 (first seen)</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -813,12 +817,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Fertilisers</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -828,62 +832,106 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>location not stated</t>
-        </is>
-      </c>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>Danske Bank</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 (first seen)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>location not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>BT Group</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Junior Project Manager</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>entry-level title</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Telecom</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Open job</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -891,10 +939,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1209,7 +1258,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1392,22 +1441,22 @@
         <v>397</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>not in English: 1, outside Europe: 1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1774,20 +1823,20 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 3+ yrs: 1</t>
+          <t>experience: requires 8+ yrs: 1, experience: requires 3-5 yrs: 1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1995,7 +2044,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>2</v>
@@ -2009,7 +2058,7 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2257,7 +2306,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
@@ -2347,7 +2396,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
@@ -2365,7 +2414,7 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.aviva.co.uk/</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2526,22 +2575,22 @@
         <v>311</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>experience: no entry-level signal: 2, outside Europe: 1</t>
+          <t>outside Europe: 6, experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2609,22 +2658,18 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2695,7 +2740,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
@@ -2709,7 +2754,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2930,7 +2975,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.blablacar.com/careers</t>
+          <t>HTTPError: 404 Client Error: Not Found for url: https://www.blablacar.co.uk/careers</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -3117,14 +3162,14 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>0</v>
@@ -3135,7 +3180,7 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3211,21 +3256,25 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 3</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3293,10 +3342,10 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>0</v>
@@ -3307,7 +3356,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3338,7 +3387,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>1</v>
@@ -3352,7 +3401,7 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3389,19 +3438,15 @@
         <v>2</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 1, experience: mid level: 1</t>
-        </is>
-      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3432,7 +3477,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>1</v>
@@ -3446,7 +3491,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3633,7 +3678,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3715,7 +3760,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3729,7 +3774,7 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3895,18 +3940,22 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 2</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4067,7 +4116,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>0</v>
@@ -4126,7 +4175,7 @@
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4284,7 +4333,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>3</v>
@@ -4298,7 +4347,7 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4464,7 +4513,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>0</v>
@@ -4478,7 +4527,7 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4505,14 +4554,14 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>0</v>
@@ -4523,7 +4572,7 @@
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4793,7 +4842,7 @@
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4824,7 +4873,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>2</v>
@@ -4838,7 +4887,7 @@
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5160,7 +5209,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5238,25 +5287,29 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -5301,7 +5354,7 @@
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5377,10 +5430,10 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>0</v>
@@ -5422,7 +5475,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>0</v>
@@ -5436,7 +5489,7 @@
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5733,14 +5786,14 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>0</v>
@@ -5751,7 +5804,7 @@
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6042,7 +6095,7 @@
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -6341,7 +6394,7 @@
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -7044,25 +7097,21 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -7138,7 +7187,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7152,7 +7201,7 @@
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7265,21 +7314,25 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>older than limit: 1</t>
+        </is>
+      </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7355,7 +7408,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -8080,21 +8133,21 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>23</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -8170,7 +8223,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>1</v>
@@ -8184,7 +8237,7 @@
       <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -8348,7 +8401,7 @@
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -8596,7 +8649,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>1</v>
@@ -8805,7 +8858,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -8819,7 +8872,7 @@
       <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8887,7 +8940,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>2</v>
@@ -8901,7 +8954,7 @@
       <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8969,7 +9022,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>5</v>
@@ -8983,7 +9036,7 @@
       <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -9059,10 +9112,10 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G189" s="2" t="n">
         <v>0</v>
@@ -9073,7 +9126,7 @@
       <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -9215,7 +9268,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>1</v>
@@ -9229,7 +9282,7 @@
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -9356,7 +9409,7 @@
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -9559,22 +9612,18 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G201" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I201" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I201" s="2" t="inlineStr"/>
       <c r="J201" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9645,21 +9694,25 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H203" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I203" s="2" t="inlineStr"/>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -9690,10 +9743,10 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F204" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G204" s="2" t="n">
         <v>0</v>
@@ -9704,7 +9757,7 @@
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -10034,7 +10087,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -10169,7 +10222,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>11</v>
@@ -10183,7 +10236,7 @@
       <c r="I215" s="2" t="inlineStr"/>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -10251,25 +10304,25 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G217" s="2" t="n">
         <v>4</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2, experience: senior title: 1</t>
+          <t>outside Europe: 4</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -10861,7 +10914,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>10</v>
@@ -10875,7 +10928,7 @@
       <c r="I231" s="2" t="inlineStr"/>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K231" s="2" t="inlineStr">
@@ -10951,25 +11004,21 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G233" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H233" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I233" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 2, experience: requires 3-4 yrs: 1</t>
-        </is>
-      </c>
+      <c r="I233" s="2" t="inlineStr"/>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -11051,7 +11100,7 @@
       <c r="I235" s="2" t="inlineStr"/>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr">
@@ -11119,10 +11168,10 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G237" s="2" t="n">
         <v>1</v>
@@ -11132,7 +11181,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -11303,7 +11352,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11317,7 +11366,7 @@
       <c r="I241" s="2" t="inlineStr"/>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -11565,25 +11614,25 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1, experience: no entry-level signal: 1, experience: requires 5-7 yrs: 1, experience: requires 5+ yrs: 1, experience: senior title: 1, experience: requires 8+ yrs: 1</t>
+          <t>outside Europe: 3, experience: requires 5+ yrs: 1, experience: internship: 1</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K247" s="2" t="inlineStr">
@@ -11749,7 +11798,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -11763,7 +11812,7 @@
       <c r="I251" s="2" t="inlineStr"/>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K251" s="2" t="inlineStr">
@@ -12017,7 +12066,7 @@
       <c r="I257" s="2" t="inlineStr"/>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr">
@@ -12093,21 +12142,25 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I259" s="2" t="inlineStr"/>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
@@ -12134,25 +12187,29 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F260" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H260" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I260" s="2" t="inlineStr"/>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 2</t>
+        </is>
+      </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -12318,18 +12375,22 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F264" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G264" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G264" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I264" s="2" t="inlineStr"/>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1, experience: requires 5+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12445,7 +12506,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>1</v>
@@ -12631,7 +12692,7 @@
       <c r="I271" s="2" t="inlineStr"/>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K271" s="2" t="inlineStr">
@@ -12750,19 +12811,15 @@
         <v>1</v>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H274" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I274" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I274" s="2" t="inlineStr"/>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr">
@@ -13174,21 +13231,25 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 8-10 yrs: 1</t>
+        </is>
+      </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr">
@@ -13389,7 +13450,7 @@
       <c r="I289" s="2" t="inlineStr"/>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr">
@@ -13965,25 +14026,21 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F303" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G303" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H303" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I303" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 3, outside Europe: 2</t>
-        </is>
-      </c>
+      <c r="I303" s="2" t="inlineStr"/>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>found via job search page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr">
@@ -14366,7 +14423,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14380,7 +14437,7 @@
       <c r="I312" s="2" t="inlineStr"/>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K312" s="2" t="inlineStr">
@@ -14549,19 +14606,15 @@
         <v>47</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H316" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I316" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I316" s="2" t="inlineStr"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14841,18 +14894,22 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F323" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G323" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H323" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I323" s="2" t="inlineStr"/>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J323" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14886,7 +14943,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>2</v>
@@ -14899,12 +14956,12 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 10+ yrs: 1</t>
+          <t>experience: internship: 1</t>
         </is>
       </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K324" s="2" t="inlineStr">
@@ -14935,7 +14992,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -14976,29 +15033,25 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F326" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G326" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H326" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I326" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I326" s="2" t="inlineStr"/>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>no job platform detected; reading page directly</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -15074,7 +15127,7 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F328" s="2" t="n">
         <v>39</v>
@@ -15088,7 +15141,7 @@
       <c r="I328" s="2" t="inlineStr"/>
       <c r="J328" s="2" t="inlineStr">
         <is>
-          <t>found on careers page</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K328" s="2" t="inlineStr">
@@ -15164,10 +15217,10 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F330" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G330" s="2" t="n">
         <v>0</v>
@@ -15209,7 +15262,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>2</v>
@@ -15302,19 +15355,15 @@
         <v>34</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I333" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 4-6 yrs: 1, experience: requires 6+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I333" s="2" t="inlineStr"/>
       <c r="J333" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15354,19 +15403,19 @@
         <v>2</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1, experience: no entry-level signal: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>SuccessFactors career site</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K334" s="2" t="inlineStr">

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -148,8 +148,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Newmatches" displayName="Newmatches" ref="A1:J2" headerRowCount="1">
-  <autoFilter ref="A1:J2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Newmatches" displayName="Newmatches" ref="A1:J3" headerRowCount="1">
+  <autoFilter ref="A1:J3"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Company"/>
     <tableColumn id="2" name="Job title"/>
@@ -167,8 +167,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J6" headerRowCount="1">
-  <autoFilter ref="A1:J6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J8" headerRowCount="1">
+  <autoFilter ref="A1:J8"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Company"/>
     <tableColumn id="2" name="Job title"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -564,58 +564,107 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Graduate Project Manager</t>
+          <t>Automation &amp; AI Project Manager (f/m/div.)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GB - Edinburgh; United Kingdom</t>
+          <t>Lisboa, Lisboa, Portugal</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Industrial technology</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>GBS People Services – Project Administrator (f/m/div.)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa, , Portugal</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>entry-level title</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; defence</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Industrial technology</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Open job</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -626,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -696,37 +745,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Graduate Project Manager</t>
+          <t>Automation &amp; AI Project Manager (f/m/div.)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GB - Edinburgh; United Kingdom</t>
+          <t>Lisboa, Lisboa, Portugal</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>entry-level title</t>
+          <t>entry level</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Aerospace &amp; defence</t>
+          <t>Industrial technology</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -736,7 +785,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -744,37 +793,37 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Customer Project Officer (a)</t>
+          <t>GBS People Services – Project Administrator (f/m/div.)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Madrid; Spain</t>
+          <t>Lisboa, , Portugal</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>entry-level wording</t>
+          <t>entry level</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Health technology</t>
+          <t>Industrial technology</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -784,7 +833,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -792,22 +841,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Yara</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Associate Product Manager</t>
+          <t>Graduate Project Manager</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Porsgrunn, NO</t>
+          <t>GB - Edinburgh; United Kingdom</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -817,12 +866,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Fertilisers</t>
+          <t>Aerospace &amp; defence</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -832,7 +881,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -840,33 +889,37 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Danske Bank</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
+          <t>Customer Project Officer (a)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Madrid; Spain</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 (first seen)</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>entry-level title</t>
+          <t>entry-level wording</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Health technology</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -876,62 +929,154 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>location not stated</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Yara</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Associate Product Manager</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Porsgrunn, NO</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Fertilisers</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Danske Bank</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 (first seen)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>location not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>BT Group</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Junior Project Manager</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>entry-level title</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Telecom</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Open job</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -940,10 +1085,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1258,7 +1405,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1438,22 +1585,18 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>19</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1, outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -1669,7 +1812,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>SSLError: HTTPSConnectionPool(host='careers.alcon.com', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING</t>
+          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.alcon.com', port=443): Max retries exceeded with url: / (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='careers.alcon.co</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1823,22 +1966,18 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 8+ yrs: 1, experience: requires 3-5 yrs: 1</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2306,7 +2445,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
@@ -2319,7 +2458,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1</t>
+          <t>experience: requires 4-6 yrs: 1</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2389,11 +2528,7 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>generic</t>
-        </is>
-      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>error</t>
@@ -2417,11 +2552,7 @@
           <t>HTTPError: 403 Client Error: Forbidden for url: https://careers.aviva.co.uk/</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.aviva.co.uk/</t>
-        </is>
-      </c>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2572,20 +2703,20 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 6, experience: no entry-level signal: 1</t>
+          <t>outside Europe: 3, experience: no entry-level signal: 1, experience: senior title: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2658,18 +2789,22 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 5+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2740,7 +2875,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
@@ -3166,18 +3301,22 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 3-5 yrs: 1</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3256,22 +3395,18 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 3</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3342,7 +3477,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>3</v>
@@ -3387,18 +3522,22 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3432,7 +3571,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>2</v>
@@ -3477,7 +3616,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>1</v>
@@ -3678,7 +3817,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
@@ -3760,7 +3899,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -3940,22 +4079,18 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 2</t>
-        </is>
-      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -4116,7 +4251,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>0</v>
@@ -4161,7 +4296,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -4333,7 +4468,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>3</v>
@@ -4554,25 +4689,29 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4599,25 +4738,29 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1, experience: requires 3+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4873,7 +5016,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>2</v>
@@ -5209,7 +5352,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -5297,16 +5440,12 @@
         <v>1</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5340,18 +5479,22 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5430,18 +5573,22 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5475,7 +5622,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>0</v>
@@ -6380,7 +6527,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>0</v>
@@ -7103,12 +7250,16 @@
         <v>3</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7187,7 +7338,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7314,7 +7465,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>8</v>
@@ -7327,7 +7478,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>older than limit: 1</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -7408,7 +7559,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -8133,18 +8284,22 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I166" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 2, experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8858,7 +9013,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -8940,7 +9095,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>2</v>
@@ -9063,25 +9218,29 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 3+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -9271,7 +9430,7 @@
         <v>21</v>
       </c>
       <c r="F193" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" s="2" t="n">
         <v>0</v>
@@ -9612,10 +9771,10 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G201" s="2" t="n">
         <v>0</v>
@@ -9700,16 +9859,12 @@
         <v>1</v>
       </c>
       <c r="G203" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -9743,7 +9898,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>1</v>
@@ -10087,7 +10242,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -10304,20 +10459,20 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>49</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 4</t>
+          <t>outside Europe: 1, experience: senior title: 1</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -11004,7 +11159,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>3</v>
@@ -11086,7 +11241,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -11168,22 +11323,18 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H237" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I237" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I237" s="2" t="inlineStr"/>
       <c r="J237" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11352,7 +11503,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11614,20 +11765,20 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 3, experience: requires 5+ yrs: 1, experience: internship: 1</t>
+          <t>experience: requires 5+ yrs: 1, outside Europe: 1</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -11798,7 +11949,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -12052,7 +12203,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>4</v>
@@ -12142,22 +12293,18 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I259" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I259" s="2" t="inlineStr"/>
       <c r="J259" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12187,29 +12334,25 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F260" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G260" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H260" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I260" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 2</t>
-        </is>
-      </c>
+      <c r="I260" s="2" t="inlineStr"/>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -12375,20 +12518,20 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F264" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G264" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G264" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>not in English: 1, experience: requires 5+ yrs: 1</t>
+          <t>experience: requires 5+ yrs: 1, experience: requires 3-5 yrs: 1, experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -12509,7 +12652,7 @@
         <v>26</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G267" s="2" t="n">
         <v>0</v>
@@ -12805,7 +12948,7 @@
         </is>
       </c>
       <c r="E274" s="2" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F274" s="2" t="n">
         <v>1</v>
@@ -13231,7 +13374,7 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F284" s="2" t="n">
         <v>1</v>
@@ -13244,7 +13387,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 8-10 yrs: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
@@ -14026,7 +14169,7 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F303" s="2" t="n">
         <v>4</v>
@@ -14112,7 +14255,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E305" s="2" t="n">
@@ -14130,7 +14273,7 @@
       <c r="I305" s="2" t="inlineStr"/>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://totalenergies.com/careers</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr">
@@ -14423,7 +14566,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>0</v>
@@ -14603,7 +14746,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>0</v>
@@ -14943,22 +15086,18 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I324" s="2" t="inlineStr">
-        <is>
-          <t>experience: internship: 1</t>
-        </is>
-      </c>
+      <c r="I324" s="2" t="inlineStr"/>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14992,7 +15131,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -15127,18 +15266,22 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I328" s="2" t="inlineStr"/>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 2</t>
+        </is>
+      </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15217,7 +15360,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>0</v>
@@ -15262,10 +15405,10 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F331" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G331" s="2" t="n">
         <v>0</v>
@@ -15352,18 +15495,22 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F333" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I333" s="2" t="inlineStr"/>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15397,22 +15544,18 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I334" s="2" t="inlineStr"/>
       <c r="J334" s="2" t="inlineStr">
         <is>
           <t>remembered</t>

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -148,8 +148,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Newmatches" displayName="Newmatches" ref="A1:J3" headerRowCount="1">
-  <autoFilter ref="A1:J3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Newmatches" displayName="Newmatches" ref="A1:J2" headerRowCount="1">
+  <autoFilter ref="A1:J2"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Company"/>
     <tableColumn id="2" name="Job title"/>
@@ -167,8 +167,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J8" headerRowCount="1">
-  <autoFilter ref="A1:J8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J9" headerRowCount="1">
+  <autoFilter ref="A1:J9"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Company"/>
     <tableColumn id="2" name="Job title"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -564,37 +564,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Reckitt</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Automation &amp; AI Project Manager (f/m/div.)</t>
+          <t>Artwork &amp; Project Coordinator</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Lisboa, Lisboa, Portugal</t>
+          <t>Warszawa, Mazovia Province, PL, N/A</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>entry-level title</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Industrial technology</t>
+          <t>Consumer health &amp; hygiene</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -604,67 +604,18 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Bosch</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>GBS People Services – Project Administrator (f/m/div.)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Lisboa, , Portugal</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>entry level</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Industrial technology</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Open job</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -675,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -745,37 +696,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Reckitt</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Automation &amp; AI Project Manager (f/m/div.)</t>
+          <t>Artwork &amp; Project Coordinator</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Lisboa, Lisboa, Portugal</t>
+          <t>Warszawa, Mazovia Province, PL, N/A</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>entry-level title</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Industrial technology</t>
+          <t>Consumer health &amp; hygiene</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -785,7 +736,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -798,17 +749,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>GBS People Services – Project Administrator (f/m/div.)</t>
+          <t>Automation &amp; AI Project Manager (f/m/div.)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Lisboa, , Portugal</t>
+          <t>Lisboa, Lisboa, Portugal</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -841,17 +792,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Graduate Project Manager</t>
+          <t>GBS People Services – Project Administrator (f/m/div.)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>GB - Edinburgh; United Kingdom</t>
+          <t>Lisboa, , Portugal</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -861,17 +812,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>entry-level title</t>
+          <t>entry level</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Aerospace &amp; defence</t>
+          <t>Industrial technology</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -881,7 +832,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -889,37 +840,37 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Customer Project Officer (a)</t>
+          <t>Graduate Project Manager</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Madrid; Spain</t>
+          <t>GB - Edinburgh; United Kingdom</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>entry-level wording</t>
+          <t>entry-level title</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Health technology</t>
+          <t>Aerospace &amp; defence</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -929,7 +880,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -937,37 +888,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Yara</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Associate Product Manager</t>
+          <t>Customer Project Officer (a)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Porsgrunn, NO</t>
+          <t>Madrid; Spain</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>entry-level title</t>
+          <t>entry-level wording</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Fertilisers</t>
+          <t>Health technology</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -977,7 +928,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -985,18 +936,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Danske Bank</t>
+          <t>Yara</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
+          <t>Associate Product Manager</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Porsgrunn, NO</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 (first seen)</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1006,12 +961,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Fertilisers</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1021,62 +976,106 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>location not stated</t>
-        </is>
-      </c>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Danske Bank</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>15 okt 2026 | LT Project Coordinator in Markets Services</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 (first seen)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>entry-level title</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Open job</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>location not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>BT Group</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Junior Project Manager</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>entry-level title</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Telecom</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Open job</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1087,10 +1086,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1585,18 +1585,22 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>19</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -1966,18 +1970,22 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2445,22 +2453,18 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 4-6 yrs: 1</t>
-        </is>
-      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2703,20 +2707,20 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 3, experience: no entry-level signal: 1, experience: senior title: 1</t>
+          <t>outside Europe: 2, experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2789,22 +2793,18 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
@@ -3307,14 +3307,14 @@
         <v>2</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 3-5 yrs: 1</t>
+          <t>experience: requires 5+ yrs: 1, experience: requires 3+ yrs: 1</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3395,18 +3395,22 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 3, experience: senior level: 1</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3477,18 +3481,22 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3525,19 +3533,15 @@
         <v>36</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3571,7 +3575,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>2</v>
@@ -3616,10 +3620,10 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>0</v>
@@ -3899,7 +3903,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>0</v>
@@ -4079,7 +4083,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>2</v>
@@ -4251,7 +4255,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>0</v>
@@ -4296,7 +4300,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -4419,25 +4423,29 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4468,7 +4476,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>3</v>
@@ -4689,29 +4697,25 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4742,20 +4746,20 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>experience: senior title: 1, experience: requires 3+ yrs: 1</t>
+          <t>experience: requires 3-5 yrs: 1</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5016,18 +5020,22 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5479,7 +5487,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>1</v>
@@ -5492,7 +5500,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>not in English: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -5573,22 +5581,18 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7244,22 +7248,18 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>not in English: 1</t>
-        </is>
-      </c>
+      <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7465,22 +7465,18 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -7559,7 +7555,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>0</v>
@@ -8284,22 +8280,18 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>25</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 2, experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -8378,10 +8370,10 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G168" s="2" t="n">
         <v>0</v>
@@ -8804,7 +8796,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>1</v>
@@ -9013,7 +9005,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>10</v>
@@ -9177,7 +9169,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>5</v>
@@ -9235,7 +9227,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 3+ yrs: 1</t>
+          <t>older than limit: 1</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
@@ -9271,7 +9263,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>2</v>
@@ -9771,10 +9763,10 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G201" s="2" t="n">
         <v>0</v>
@@ -9853,7 +9845,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>1</v>
@@ -10242,7 +10234,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -10377,10 +10369,10 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F215" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G215" s="2" t="n">
         <v>0</v>
@@ -10459,20 +10451,20 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 1, experience: senior title: 1</t>
+          <t>outside Europe: 1</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -11069,7 +11061,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>10</v>
@@ -11329,12 +11321,16 @@
         <v>2</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I237" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11503,7 +11499,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>2</v>
@@ -11768,7 +11764,7 @@
         <v>311</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G247" s="2" t="n">
         <v>2</v>
@@ -11949,7 +11945,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>0</v>
@@ -12203,7 +12199,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>4</v>
@@ -12293,10 +12289,10 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G259" s="2" t="n">
         <v>0</v>
@@ -12518,20 +12514,20 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H264" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 5+ yrs: 1, experience: requires 3-5 yrs: 1, experience: no entry-level signal: 1</t>
+          <t>not in English: 1</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -12649,18 +12645,22 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I267" s="2" t="inlineStr"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>experience: no entry-level signal: 1</t>
+        </is>
+      </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12948,18 +12948,22 @@
         </is>
       </c>
       <c r="E274" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F274" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G274" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G274" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H274" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -13374,22 +13378,18 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I284" s="2" t="inlineStr"/>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14169,7 +14169,7 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F303" s="2" t="n">
         <v>4</v>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E305" s="2" t="n">
@@ -14273,7 +14273,7 @@
       <c r="I305" s="2" t="inlineStr"/>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 403 Client Error: Forbidden for url: https://totalenergies.com/careers</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr">
@@ -14566,18 +14566,22 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F312" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G312" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H312" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I312" s="2" t="inlineStr"/>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14746,7 +14750,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>0</v>
@@ -15037,22 +15041,18 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G323" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H323" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I323" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I323" s="2" t="inlineStr"/>
       <c r="J323" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15086,18 +15086,22 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I324" s="2" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>experience: senior title: 1</t>
+        </is>
+      </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15131,7 +15135,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -15266,20 +15270,20 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 2</t>
+          <t>experience: senior title: 1</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr">
@@ -15360,7 +15364,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>0</v>
@@ -15405,7 +15409,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>1</v>
@@ -15495,22 +15499,18 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F333" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H333" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I333" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I333" s="2" t="inlineStr"/>
       <c r="J333" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15544,18 +15544,22 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I334" s="2" t="inlineStr"/>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>experience: requires 3+ yrs: 1</t>
+        </is>
+      </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
           <t>remembered</t>

--- a/output/job_matches.xlsx
+++ b/output/job_matches.xlsx
@@ -148,8 +148,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Newmatches" displayName="Newmatches" ref="A1:J2" headerRowCount="1">
-  <autoFilter ref="A1:J2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Recentmatches" displayName="Recentmatches" ref="A1:J9" headerRowCount="1">
+  <autoFilter ref="A1:J9"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Company"/>
     <tableColumn id="2" name="Job title"/>
@@ -167,26 +167,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Recentmatches" displayName="Recentmatches" ref="A1:J9" headerRowCount="1">
-  <autoFilter ref="A1:J9"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="Company"/>
-    <tableColumn id="2" name="Job title"/>
-    <tableColumn id="3" name="Location"/>
-    <tableColumn id="4" name="Posted"/>
-    <tableColumn id="5" name="Experience"/>
-    <tableColumn id="6" name="HQ country"/>
-    <tableColumn id="7" name="Sector"/>
-    <tableColumn id="8" name="Link"/>
-    <tableColumn id="9" name="Found on"/>
-    <tableColumn id="10" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Coverage" displayName="Coverage" ref="A1:K337" headerRowCount="1">
   <autoFilter ref="A1:K337"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Company"/>
@@ -494,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -561,62 +542,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Reckitt</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Artwork &amp; Project Coordinator</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Warszawa, Mazovia Province, PL, N/A</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>entry-level title</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Consumer health &amp; hygiene</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Open job</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -1585,22 +1512,18 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -1816,7 +1739,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>ConnectTimeout: HTTPSConnectionPool(host='careers.alcon.com', port=443): Max retries exceeded with url: / (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='careers.alcon.co</t>
+          <t>SSLError: HTTPSConnectionPool(host='careers.alcon.com', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1970,7 +1893,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
@@ -1983,7 +1906,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>not in English: 1</t>
+          <t>experience: no entry-level signal: 1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2453,7 +2376,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -2707,22 +2630,18 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 2, experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -2793,18 +2712,22 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3110,7 +3033,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>HTTPError: 404 Client Error: Not Found for url: https://www.blablacar.co.uk/careers</t>
+          <t>HTTPError: 403 Client Error: Forbidden for url: https://www.blablacar.com/careers</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -3297,29 +3220,25 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1, experience: requires 3+ yrs: 1</t>
-        </is>
-      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3395,20 +3314,20 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>25</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>outside Europe: 3, experience: senior level: 1</t>
+          <t>outside Europe: 2</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3481,22 +3400,18 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -3530,7 +3445,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>0</v>
@@ -3575,7 +3490,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>2</v>
@@ -3620,7 +3535,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>0</v>
@@ -4083,7 +3998,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>2</v>
@@ -4255,7 +4170,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>0</v>
@@ -4300,7 +4215,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>3</v>
@@ -4423,29 +4338,25 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4476,7 +4387,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>3</v>
@@ -4656,7 +4567,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>0</v>
@@ -4746,20 +4657,20 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 3-5 yrs: 1</t>
+          <t>experience: senior title: 2, experience: requires 4+ yrs: 1</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5020,22 +4931,18 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5438,14 +5345,14 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>0</v>
@@ -5456,7 +5363,7 @@
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -5487,7 +5394,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>1</v>
@@ -5581,18 +5488,22 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F103" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G103" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>not in English: 1</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -5937,14 +5848,14 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>0</v>
@@ -5955,7 +5866,7 @@
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>remembered</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6531,7 +6442,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7159,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>2</v>
@@ -7338,7 +7249,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>6</v>
@@ -7465,7 +7376,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>8</v>
@@ -8280,10 +8191,10 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G166" s="2" t="n">
         <v>0</v>
@@ -9087,7 +8998,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>2</v>
@@ -9210,29 +9121,25 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>no jobs found</t>
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t>older than limit: 1</t>
-        </is>
-      </c>
+      <c r="I188" s="2" t="inlineStr"/>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>remembered</t>
+          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -9263,7 +9170,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>2</v>
@@ -9419,7 +9326,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>0</v>
@@ -9763,7 +9670,7 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>2</v>
@@ -10234,7 +10141,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>0</v>
@@ -10451,7 +10358,7 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>46</v>
@@ -11061,10 +10968,10 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G231" s="2" t="n">
         <v>0</v>
@@ -11151,7 +11058,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>3</v>
@@ -11233,7 +11140,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>0</v>
@@ -11315,22 +11222,18 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I237" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I237" s="2" t="inlineStr"/>
       <c r="J237" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -11499,10 +11402,10 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F241" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G241" s="2" t="n">
         <v>0</v>
@@ -11667,7 +11570,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>no jobs found</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E245" s="2" t="n">
@@ -11685,7 +11588,7 @@
       <c r="I245" s="2" t="inlineStr"/>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>page may need a browser (JavaScript); add the platform in companies.csv</t>
+          <t>RetryError: HTTPSConnectionPool(host='careers.rimac-group.com', port=443): Max retries exceeded with url: / (Caused by ResponseError('too many 500 error responses'))</t>
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr">
@@ -11761,22 +11664,18 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I247" s="2" t="inlineStr">
-        <is>
-          <t>experience: requires 5+ yrs: 1, outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I247" s="2" t="inlineStr"/>
       <c r="J247" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12199,7 +12098,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>4</v>
@@ -12289,18 +12188,22 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H259" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I259" s="2" t="inlineStr"/>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12514,10 +12417,10 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G264" s="2" t="n">
         <v>1</v>
@@ -12527,7 +12430,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>not in English: 1</t>
+          <t>experience: requires 2-5 yrs: 1</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -12651,16 +12554,12 @@
         <v>1</v>
       </c>
       <c r="G267" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H267" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I267" s="2" t="inlineStr">
-        <is>
-          <t>experience: no entry-level signal: 1</t>
-        </is>
-      </c>
+      <c r="I267" s="2" t="inlineStr"/>
       <c r="J267" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -12954,16 +12853,12 @@
         <v>2</v>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H274" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I274" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I274" s="2" t="inlineStr"/>
       <c r="J274" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -13378,18 +13273,22 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14169,7 +14068,7 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F303" s="2" t="n">
         <v>4</v>
@@ -14566,22 +14465,18 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G312" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H312" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I312" s="2" t="inlineStr">
-        <is>
-          <t>outside Europe: 1</t>
-        </is>
-      </c>
+      <c r="I312" s="2" t="inlineStr"/>
       <c r="J312" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -14750,18 +14645,22 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F316" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H316" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I316" s="2" t="inlineStr"/>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15092,16 +14991,12 @@
         <v>1</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I324" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I324" s="2" t="inlineStr"/>
       <c r="J324" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15135,7 +15030,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>0</v>
@@ -15270,22 +15165,18 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I328" s="2" t="inlineStr">
-        <is>
-          <t>experience: senior title: 1</t>
-        </is>
-      </c>
+      <c r="I328" s="2" t="inlineStr"/>
       <c r="J328" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15364,18 +15255,22 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F330" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G330" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H330" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I330" s="2" t="inlineStr"/>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>outside Europe: 1</t>
+        </is>
+      </c>
       <c r="J330" s="2" t="inlineStr">
         <is>
           <t>remembered</t>
@@ -15409,7 +15304,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>1</v>
@@ -15499,10 +15394,10 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G333" s="2" t="n">
         <v>0</v>
@@ -15544,20 +15439,20 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H334" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>experience: requires 3+ yrs: 1</t>
+          <t>experience: senior title: 1, outside Europe: 1</t>
         </is>
       </c>
       <c r="J334" s="2" t="inlineStr">
